--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="536">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="543">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1638,6 +1638,27 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1331-064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0887-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1334-066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0000-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1333-303</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2622,63 +2643,137 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I9" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="23" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="27" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3659,11 +3754,11 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="543">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="587">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1628,6 +1628,27 @@
     <x:t>61-2-2026-1320-600</x:t>
   </x:si>
   <x:si>
+    <x:t>AL S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FB-0878-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1354-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0877-18(ren)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1340-327</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -1640,12 +1661,69 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>LUCERO R. ALBARACIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Balintawak, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1307-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1352-743</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0884-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1364-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0879-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1344-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS-4878-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0881-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1342-435</x:t>
+  </x:si>
+  <x:si>
     <x:t>REY S. BURBURAN</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
     <x:t>MS9/FV-0887-18</x:t>
   </x:si>
   <x:si>
@@ -1659,6 +1737,60 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1333-303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCHER C COTINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Sto. Nino, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1347-156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHARLO F  SALUMAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1363-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLAUDIO  E. ELNAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1348-671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWIN M SAGAYNO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1349-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAMON M SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-SROPIX-16133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1350-437</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2625,19 +2757,19 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>25</x:v>
@@ -2648,34 +2780,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>536</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>537</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>539</x:v>
-      </x:c>
       <x:c r="H9" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I9" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>25</x:v>
@@ -2686,7 +2818,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>536</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>15</x:v>
@@ -2701,93 +2833,584 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C11" s="15" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46076.1139583333</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1216146</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>46090.1919444444</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46077.2598726852</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1216158</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>46090.2758680556</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46072.1089467593</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1216152</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>46090.2365046296</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.0792939815</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1216150</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46090.220787037</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I23" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="23" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="24" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="27" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B31" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="31" t="s"/>
+      <x:c r="F31" s="32" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3751,14 +4374,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B26:F26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="587">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="591">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1782,6 +1782,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1349-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PONCIANO O. SINDAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Samboang, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ponciano O. Sinday</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1365-581</x:t>
   </x:si>
   <x:si>
     <x:t>RAMON M SILVA</x:t>
@@ -3318,100 +3330,137 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="15" t="s">
-        <x:v>548</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="F23" s="15" t="s">
-        <x:v>585</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="G23" s="15" t="s">
-        <x:v>586</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I24" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L24" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="21" t="s">
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="23" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="24" t="s">
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="23" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="s">
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="28" t="s"/>
       <x:c r="D29" s="28" t="s"/>
       <x:c r="E29" s="28" t="s"/>
       <x:c r="F29" s="29" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C30" s="28" t="s"/>
       <x:c r="D30" s="28" t="s"/>
       <x:c r="E30" s="28" t="s"/>
       <x:c r="F30" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C31" s="31" t="s"/>
-      <x:c r="D31" s="31" t="s"/>
-      <x:c r="E31" s="31" t="s"/>
-      <x:c r="F31" s="32" t="n">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C32" s="31" t="s"/>
+      <x:c r="D32" s="31" t="s"/>
+      <x:c r="E32" s="31" t="s"/>
+      <x:c r="F32" s="32" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4377,12 +4426,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="591">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1628,6 +1628,18 @@
     <x:t>61-2-2026-1320-600</x:t>
   </x:si>
   <x:si>
+    <x:t>ARTURO D ANTONIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, San Carlos, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17-SROPIX-11057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1346-185</x:t>
+  </x:si>
+  <x:si>
     <x:t>AL S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -1704,6 +1716,24 @@
   </x:si>
   <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0882-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1369-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1077-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1367-348</x:t>
   </x:si>
   <x:si>
     <x:t>MS-4878-23</x:t>
@@ -2751,7 +2781,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
         <x:v>532</x:v>
@@ -2769,19 +2799,19 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46058</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>25</x:v>
@@ -2792,34 +2822,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>532</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
-        <x:v>536</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F9" s="15" t="s">
-        <x:v>537</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>538</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46072.0333449074</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I9" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>25</x:v>
@@ -2830,7 +2860,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>539</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>15</x:v>
@@ -2845,19 +2875,19 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>25</x:v>
@@ -2883,19 +2913,19 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>25</x:v>
@@ -2921,19 +2951,19 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>25</x:v>
@@ -2944,34 +2974,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>547</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>25</x:v>
@@ -2982,34 +3012,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>547</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3020,34 +3050,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
-        <x:v>554</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3058,34 +3088,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3096,34 +3126,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>554</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3134,34 +3164,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>568</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3169,10 +3199,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
@@ -3187,19 +3217,19 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3207,7 +3237,7 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B20" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
         <x:v>573</x:v>
@@ -3216,28 +3246,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
         <x:v>574</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="G20" s="15" t="s">
         <x:v>575</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>576</x:v>
-      </x:c>
       <x:c r="H20" s="17">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3245,37 +3275,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B21" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>577</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="D21" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
         <x:v>578</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>580</x:v>
-      </x:c>
       <x:c r="H21" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3286,34 +3316,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="15" t="s">
-        <x:v>548</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="F22" s="15" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>583</x:v>
-      </x:c>
       <x:c r="H22" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3324,34 +3354,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>584</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="D23" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="15" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="G23" s="15" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>587</x:v>
-      </x:c>
       <x:c r="H23" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3362,13 +3392,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>588</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D24" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="15" t="s">
-        <x:v>548</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F24" s="15" t="s">
         <x:v>589</x:v>
@@ -3377,94 +3407,215 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="21" t="s">
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I25" s="18">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K25" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L25" s="20">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I26" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K26" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L26" s="20">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I27" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K27" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L27" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="23" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="24" t="s">
+      <x:c r="C30" s="22" t="s"/>
+      <x:c r="D30" s="22" t="s"/>
+      <x:c r="E30" s="23" t="s"/>
+      <x:c r="F30" s="23" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="s">
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="27" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C33" s="28" t="s"/>
+      <x:c r="D33" s="28" t="s"/>
+      <x:c r="E33" s="28" t="s"/>
+      <x:c r="F33" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="27" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="27" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
+      <x:c r="C35" s="28" t="s"/>
+      <x:c r="D35" s="28" t="s"/>
+      <x:c r="E35" s="28" t="s"/>
+      <x:c r="F35" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="30" t="s">
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C32" s="31" t="s"/>
-      <x:c r="D32" s="31" t="s"/>
-      <x:c r="E32" s="31" t="s"/>
-      <x:c r="F32" s="32" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C36" s="31" t="s"/>
+      <x:c r="D36" s="31" t="s"/>
+      <x:c r="E36" s="31" t="s"/>
+      <x:c r="F36" s="32" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4423,15 +4574,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="612">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1661,6 +1661,18 @@
     <x:t>61-2-2026-1340-327</x:t>
   </x:si>
   <x:si>
+    <x:t>FEY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0886-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1332-813</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -1805,6 +1817,15 @@
     <x:t>61-2-2026-1348-671</x:t>
   </x:si>
   <x:si>
+    <x:t>EDGAR S SERENCIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24-SROPIX-16132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1351-693</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN M SAGAYNO</x:t>
   </x:si>
   <x:si>
@@ -1833,6 +1854,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1350-437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBERTO Q CORPIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Limamawan, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1361-291</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2913,19 +2946,19 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>25</x:v>
@@ -2951,19 +2984,19 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>25</x:v>
@@ -2989,19 +3022,19 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>25</x:v>
@@ -3012,34 +3045,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>551</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3050,34 +3083,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>551</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I15" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3088,7 +3121,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
@@ -3103,19 +3136,19 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3126,34 +3159,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3164,34 +3197,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>568</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3202,34 +3235,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>571</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>572</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3240,34 +3273,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
-        <x:v>574</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>575</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I20" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3278,34 +3311,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D21" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
-        <x:v>576</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F21" s="15" t="s">
-        <x:v>577</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>578</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I21" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3313,10 +3346,10 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
@@ -3331,19 +3364,19 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3369,19 +3402,19 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I23" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3407,19 +3440,19 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I24" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
@@ -3436,28 +3469,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="15" t="s">
-        <x:v>552</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F25" s="15" t="s">
-        <x:v>592</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="G25" s="15" t="s">
-        <x:v>593</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="H25" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J25" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M25" s="15" t="s">
         <x:v>25</x:v>
@@ -3468,13 +3501,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>594</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D26" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F26" s="15" t="s">
         <x:v>596</x:v>
@@ -3483,19 +3516,19 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="H26" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>45748</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M26" s="15" t="s">
         <x:v>25</x:v>
@@ -3512,7 +3545,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="15" t="s">
-        <x:v>552</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F27" s="15" t="s">
         <x:v>599</x:v>
@@ -3521,104 +3554,215 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="H27" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>45824</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M27" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="21" t="s">
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I28" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K28" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L28" s="20">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I29" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K29" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L29" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I30" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K30" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L30" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C30" s="22" t="s"/>
-      <x:c r="D30" s="22" t="s"/>
-      <x:c r="E30" s="23" t="s"/>
-      <x:c r="F30" s="23" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="24" t="s">
+      <x:c r="C33" s="22" t="s"/>
+      <x:c r="D33" s="22" t="s"/>
+      <x:c r="E33" s="23" t="s"/>
+      <x:c r="F33" s="23" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="s">
+      <x:c r="C34" s="25" t="s"/>
+      <x:c r="D34" s="25" t="s"/>
+      <x:c r="E34" s="25" t="s"/>
+      <x:c r="F34" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C33" s="28" t="s"/>
-      <x:c r="D33" s="28" t="s"/>
-      <x:c r="E33" s="28" t="s"/>
-      <x:c r="F33" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="28" t="s"/>
       <x:c r="D35" s="28" t="s"/>
       <x:c r="E35" s="28" t="s"/>
       <x:c r="F35" s="29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="30" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="27" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C36" s="28" t="s"/>
+      <x:c r="D36" s="28" t="s"/>
+      <x:c r="E36" s="28" t="s"/>
+      <x:c r="F36" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C37" s="28" t="s"/>
+      <x:c r="D37" s="28" t="s"/>
+      <x:c r="E37" s="28" t="s"/>
+      <x:c r="F37" s="29" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C38" s="28" t="s"/>
+      <x:c r="D38" s="28" t="s"/>
+      <x:c r="E38" s="28" t="s"/>
+      <x:c r="F38" s="29" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C36" s="31" t="s"/>
-      <x:c r="D36" s="31" t="s"/>
-      <x:c r="E36" s="31" t="s"/>
-      <x:c r="F36" s="32" t="n">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C39" s="31" t="s"/>
+      <x:c r="D39" s="31" t="s"/>
+      <x:c r="E39" s="31" t="s"/>
+      <x:c r="F39" s="32" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4577,13 +4721,13 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B30:F30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="612">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1638,6 +1638,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1346-185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>none Prk.San francisco, San jose, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110622F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1359-531</x:t>
   </x:si>
   <x:si>
     <x:t>AL S. BURBURAN</x:t>
@@ -2852,7 +2864,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
         <x:v>536</x:v>
@@ -2870,19 +2882,19 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>25</x:v>
@@ -2893,34 +2905,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>536</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
-        <x:v>540</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F10" s="15" t="s">
-        <x:v>541</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>542</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46072.0333449074</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I10" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>25</x:v>
@@ -2931,7 +2943,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>543</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>15</x:v>
@@ -2946,19 +2958,19 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46071.1677662037</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I11" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216165</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46091.1948842593</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>25</x:v>
@@ -2984,19 +2996,19 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>25</x:v>
@@ -3022,19 +3034,19 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>25</x:v>
@@ -3060,19 +3072,19 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3083,34 +3095,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I15" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3121,34 +3133,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3159,7 +3171,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
@@ -3174,19 +3186,19 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I17" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3197,34 +3209,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>570</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>571</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3235,34 +3247,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>572</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3273,34 +3285,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>574</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
-        <x:v>575</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>576</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3311,34 +3323,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>577</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D21" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F21" s="15" t="s">
-        <x:v>578</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>579</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I21" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3349,34 +3361,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>577</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="15" t="s">
-        <x:v>580</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F22" s="15" t="s">
-        <x:v>581</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>582</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I22" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3384,10 +3396,10 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="D23" s="16" t="s">
         <x:v>15</x:v>
@@ -3402,19 +3414,19 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3440,19 +3452,19 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I24" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
@@ -3478,19 +3490,19 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="H25" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I25" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J25" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M25" s="15" t="s">
         <x:v>25</x:v>
@@ -3507,28 +3519,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="F26" s="15" t="s">
-        <x:v>596</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="G26" s="15" t="s">
-        <x:v>597</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="H26" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M26" s="15" t="s">
         <x:v>25</x:v>
@@ -3539,34 +3551,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>598</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="D27" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F27" s="15" t="s">
-        <x:v>599</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G27" s="15" t="s">
-        <x:v>600</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H27" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M27" s="15" t="s">
         <x:v>25</x:v>
@@ -3577,13 +3589,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>601</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D28" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="15" t="s">
-        <x:v>602</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F28" s="15" t="s">
         <x:v>603</x:v>
@@ -3592,19 +3604,19 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="H28" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>45748</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M28" s="15" t="s">
         <x:v>25</x:v>
@@ -3621,28 +3633,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F29" s="15" t="s">
-        <x:v>606</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="G29" s="15" t="s">
-        <x:v>607</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="H29" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J29" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M29" s="15" t="s">
         <x:v>25</x:v>
@@ -3653,13 +3665,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="15" t="s">
-        <x:v>608</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="D30" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F30" s="15" t="s">
         <x:v>610</x:v>
@@ -3668,103 +3680,150 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="H30" s="17">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.0763541667</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46115</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216149</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2162847222</x:v>
       </x:c>
       <x:c r="M30" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I31" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K31" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L31" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="21" t="s">
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C33" s="22" t="s"/>
-      <x:c r="D33" s="22" t="s"/>
-      <x:c r="E33" s="23" t="s"/>
-      <x:c r="F33" s="23" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="24" t="s">
+      <x:c r="C34" s="22" t="s"/>
+      <x:c r="D34" s="22" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="23" t="s"/>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B35" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C34" s="25" t="s"/>
-      <x:c r="D34" s="25" t="s"/>
-      <x:c r="E34" s="25" t="s"/>
-      <x:c r="F34" s="26" t="s">
+      <x:c r="C35" s="25" t="s"/>
+      <x:c r="D35" s="25" t="s"/>
+      <x:c r="E35" s="25" t="s"/>
+      <x:c r="F35" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C35" s="28" t="s"/>
-      <x:c r="D35" s="28" t="s"/>
-      <x:c r="E35" s="28" t="s"/>
-      <x:c r="F35" s="29" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="27" t="s">
-        <x:v>111</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="28" t="s"/>
       <x:c r="D36" s="28" t="s"/>
       <x:c r="E36" s="28" t="s"/>
       <x:c r="F36" s="29" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C37" s="28" t="s"/>
       <x:c r="D37" s="28" t="s"/>
       <x:c r="E37" s="28" t="s"/>
       <x:c r="F37" s="29" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C38" s="28" t="s"/>
       <x:c r="D38" s="28" t="s"/>
       <x:c r="E38" s="28" t="s"/>
       <x:c r="F38" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C39" s="28" t="s"/>
+      <x:c r="D39" s="28" t="s"/>
+      <x:c r="E39" s="28" t="s"/>
+      <x:c r="F39" s="29" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C40" s="28" t="s"/>
+      <x:c r="D40" s="28" t="s"/>
+      <x:c r="E40" s="28" t="s"/>
+      <x:c r="F40" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="30" t="s">
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C39" s="31" t="s"/>
-      <x:c r="D39" s="31" t="s"/>
-      <x:c r="E39" s="31" t="s"/>
-      <x:c r="F39" s="32" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C41" s="31" t="s"/>
+      <x:c r="D41" s="31" t="s"/>
+      <x:c r="E41" s="31" t="s"/>
+      <x:c r="F41" s="32" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4718,16 +4777,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B34:F34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1616,6 +1616,18 @@
     <x:t>61-2-2026-1322-666</x:t>
   </x:si>
   <x:si>
+    <x:t>LILIA R. FLORIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK 1, BINTANA, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97-1PX-18986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1378-820</x:t>
+  </x:si>
+  <x:si>
     <x:t>MERIAM MANON-OG LICAYAN</x:t>
   </x:si>
   <x:si>
@@ -1628,6 +1640,42 @@
     <x:t>61-2-2026-1320-600</x:t>
   </x:si>
   <x:si>
+    <x:t>MYRNA M MANUGAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A P-6, Lorenzo, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-3PX-3945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1381-306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILMA E BERMUDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Saging-saging, Micanaway, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-1PX-23569</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1379-115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZ CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>km. 5 lantawan drive, pasonanca, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-06868-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1384-689</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
   </x:si>
   <x:si>
@@ -1640,6 +1688,63 @@
     <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
+    <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Diplahan, Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110624G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1294-762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-110613A-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1293-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110618E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1289-791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB-GADGETZ CELLPHONE STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Dumalinao, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110616G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1295-381</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
   </x:si>
   <x:si>
@@ -1791,6 +1896,21 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1333-303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1281-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1372-847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1283-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-11-2025-1252-294</x:t>
   </x:si>
   <x:si>
     <x:t>ARCHER C COTINA</x:t>
@@ -2805,19 +2925,19 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46065.2288541667</x:v>
+        <x:v>46085.2764814815</x:v>
       </x:c>
       <x:c r="I7" s="13">
-        <x:v>46070</x:v>
+        <x:v>44879</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216140</x:v>
+        <x:v>1216175</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>390</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46084.1582175926</x:v>
+        <x:v>46093.2000115741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>25</x:v>
@@ -2826,7 +2946,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="15" t="s">
-        <x:v>111</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
         <x:v>532</x:v>
@@ -2844,19 +2964,19 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46072.3153009259</x:v>
+        <x:v>46065.2288541667</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46114</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216162</x:v>
+        <x:v>1216140</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46090.311412037</x:v>
+        <x:v>46084.1582175926</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>25</x:v>
@@ -2864,7 +2984,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
         <x:v>536</x:v>
@@ -2882,19 +3002,19 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46076.318900463</x:v>
+        <x:v>46085.3007986111</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>46074</x:v>
+        <x:v>46386</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216177</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.215162037</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>25</x:v>
@@ -2902,7 +3022,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
         <x:v>540</x:v>
@@ -2920,19 +3040,19 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46085.2858333333</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46058</x:v>
+        <x:v>46096</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216176</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46093.2057060185</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>25</x:v>
@@ -2940,37 +3060,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>540</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>544</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F11" s="15" t="s">
-        <x:v>545</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="G11" s="15" t="s">
-        <x:v>546</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46058</x:v>
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46088.179837963</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216179</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46093.2393865741</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>25</x:v>
@@ -2978,37 +3098,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>547</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
-        <x:v>548</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F12" s="15" t="s">
-        <x:v>549</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46071.1677662037</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46058</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216165</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46091.1948842593</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>25</x:v>
@@ -3016,37 +3136,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>46123</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>25</x:v>
@@ -3054,37 +3174,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46084</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3092,10 +3212,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
@@ -3110,19 +3230,19 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46058</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3130,37 +3250,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46058</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3168,37 +3288,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>568</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>46058</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3206,37 +3326,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B18" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>570</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>572</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3247,34 +3367,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>574</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>575</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3285,34 +3405,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
-        <x:v>576</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>577</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3323,34 +3443,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D21" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
-        <x:v>578</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="F21" s="15" t="s">
-        <x:v>579</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>580</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I21" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3361,34 +3481,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>581</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="F22" s="15" t="s">
-        <x:v>582</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>583</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3399,34 +3519,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>581</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D23" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="15" t="s">
-        <x:v>584</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F23" s="15" t="s">
-        <x:v>585</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="G23" s="15" t="s">
-        <x:v>586</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3434,37 +3554,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>587</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="D24" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="15" t="s">
-        <x:v>588</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F24" s="15" t="s">
-        <x:v>589</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="G24" s="15" t="s">
-        <x:v>590</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
@@ -3472,37 +3592,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="15" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="D25" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="15" t="s">
-        <x:v>592</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="F25" s="15" t="s">
-        <x:v>593</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="G25" s="15" t="s">
-        <x:v>594</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H25" s="17">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J25" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M25" s="15" t="s">
         <x:v>25</x:v>
@@ -3510,37 +3630,37 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="D26" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="15" t="s">
-        <x:v>596</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F26" s="15" t="s">
-        <x:v>597</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="G26" s="15" t="s">
-        <x:v>598</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="H26" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>46042</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M26" s="15" t="s">
         <x:v>25</x:v>
@@ -3548,37 +3668,37 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>599</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D27" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F27" s="15" t="s">
-        <x:v>600</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G27" s="15" t="s">
-        <x:v>601</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="H27" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>45824</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M27" s="15" t="s">
         <x:v>25</x:v>
@@ -3586,37 +3706,37 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B28" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>602</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D28" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="F28" s="15" t="s">
-        <x:v>603</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="G28" s="15" t="s">
-        <x:v>604</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H28" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46036</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M28" s="15" t="s">
         <x:v>25</x:v>
@@ -3624,37 +3744,37 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C29" s="15" t="s">
-        <x:v>605</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D29" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="15" t="s">
-        <x:v>606</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F29" s="15" t="s">
-        <x:v>607</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="G29" s="15" t="s">
-        <x:v>608</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="H29" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>45748</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J29" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M29" s="15" t="s">
         <x:v>25</x:v>
@@ -3662,37 +3782,37 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B30" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C30" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D30" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="F30" s="15" t="s">
-        <x:v>610</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="G30" s="15" t="s">
-        <x:v>611</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="H30" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>45824</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M30" s="15" t="s">
         <x:v>25</x:v>
@@ -3700,142 +3820,559 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E31" s="15" t="s">
-        <x:v>613</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="F31" s="15" t="s">
-        <x:v>614</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="G31" s="15" t="s">
-        <x:v>615</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="H31" s="17">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46115</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="16" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M31" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="21" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="s"/>
-      <x:c r="D34" s="22" t="s"/>
-      <x:c r="E34" s="23" t="s"/>
-      <x:c r="F34" s="23" t="s"/>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B35" s="24" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C35" s="25" t="s"/>
-      <x:c r="D35" s="25" t="s"/>
-      <x:c r="E35" s="25" t="s"/>
-      <x:c r="F35" s="26" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C36" s="28" t="s"/>
-      <x:c r="D36" s="28" t="s"/>
-      <x:c r="E36" s="28" t="s"/>
-      <x:c r="F36" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C37" s="28" t="s"/>
-      <x:c r="D37" s="28" t="s"/>
-      <x:c r="E37" s="28" t="s"/>
-      <x:c r="F37" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C38" s="28" t="s"/>
-      <x:c r="D38" s="28" t="s"/>
-      <x:c r="E38" s="28" t="s"/>
-      <x:c r="F38" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="27" t="s">
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C39" s="28" t="s"/>
-      <x:c r="D39" s="28" t="s"/>
-      <x:c r="E39" s="28" t="s"/>
-      <x:c r="F39" s="29" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="27" t="s">
+      <x:c r="C32" s="15" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I32" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K32" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L32" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I33" s="18">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L33" s="20">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I34" s="18">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K34" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L34" s="20">
+        <x:v>46093.1383912037</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C40" s="28" t="s"/>
-      <x:c r="D40" s="28" t="s"/>
-      <x:c r="E40" s="28" t="s"/>
-      <x:c r="F40" s="29" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="30" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C41" s="31" t="s"/>
-      <x:c r="D41" s="31" t="s"/>
-      <x:c r="E41" s="31" t="s"/>
-      <x:c r="F41" s="32" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C35" s="15" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46073.0262847222</x:v>
+      </x:c>
+      <x:c r="I35" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1216157</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L35" s="20">
+        <x:v>46090.267025463</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I36" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K36" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46073.0478472222</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1216153</x:v>
+      </x:c>
+      <x:c r="K37" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L37" s="20">
+        <x:v>46090.2431828704</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46073.1095023148</x:v>
+      </x:c>
+      <x:c r="I38" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
+        <x:v>1216164</x:v>
+      </x:c>
+      <x:c r="K38" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L38" s="20">
+        <x:v>46091.121087963</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46073.061099537</x:v>
+      </x:c>
+      <x:c r="I39" s="18">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
+        <x:v>1216151</x:v>
+      </x:c>
+      <x:c r="K39" s="19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L39" s="20">
+        <x:v>46090.2266435185</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I40" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K40" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L40" s="20">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I41" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K41" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L41" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I42" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K42" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L42" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C45" s="22" t="s"/>
+      <x:c r="D45" s="22" t="s"/>
+      <x:c r="E45" s="23" t="s"/>
+      <x:c r="F45" s="23" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="24" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C46" s="25" t="s"/>
+      <x:c r="D46" s="25" t="s"/>
+      <x:c r="E46" s="25" t="s"/>
+      <x:c r="F46" s="26" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="27" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C47" s="28" t="s"/>
+      <x:c r="D47" s="28" t="s"/>
+      <x:c r="E47" s="28" t="s"/>
+      <x:c r="F47" s="29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="27" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C48" s="28" t="s"/>
+      <x:c r="D48" s="28" t="s"/>
+      <x:c r="E48" s="28" t="s"/>
+      <x:c r="F48" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="27" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C50" s="28" t="s"/>
+      <x:c r="D50" s="28" t="s"/>
+      <x:c r="E50" s="28" t="s"/>
+      <x:c r="F50" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C52" s="28" t="s"/>
+      <x:c r="D52" s="28" t="s"/>
+      <x:c r="E52" s="28" t="s"/>
+      <x:c r="F52" s="29" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="s"/>
+      <x:c r="D53" s="31" t="s"/>
+      <x:c r="E53" s="31" t="s"/>
+      <x:c r="F53" s="32" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4777,17 +5314,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B34:F34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B45:F45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="667">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1911,6 +1911,39 @@
   </x:si>
   <x:si>
     <x:t>61-11-2025-1252-294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AILYN G. PANIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PURON NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06923-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1389-850</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERLINDA G. PANES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06918-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1388-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JORELYN P. SOLES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06912-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1387-457</x:t>
   </x:si>
   <x:si>
     <x:t>ARCHER C COTINA</x:t>
@@ -3972,14 +4005,12 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C35" s="15" t="s">
         <x:v>627</x:v>
       </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D35" s="16" t="s"/>
       <x:c r="E35" s="15" t="s">
         <x:v>628</x:v>
       </x:c>
@@ -3990,19 +4021,19 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="H35" s="17">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I35" s="18">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>46090.2854050926</x:v>
+      </x:c>
+      <x:c r="I35" s="17">
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="s">
+        <x:v>630</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M35" s="15" t="s">
         <x:v>25</x:v>
@@ -4010,14 +4041,12 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C36" s="15" t="s">
         <x:v>631</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D36" s="16" t="s"/>
       <x:c r="E36" s="15" t="s">
         <x:v>632</x:v>
       </x:c>
@@ -4028,19 +4057,19 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="H36" s="17">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I36" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I36" s="17">
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J36" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M36" s="15" t="s">
         <x:v>25</x:v>
@@ -4048,37 +4077,35 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" s="15" t="s">
         <x:v>635</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D37" s="16" t="s"/>
       <x:c r="E37" s="15" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
         <x:v>636</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="s">
+      <x:c r="G37" s="15" t="s">
         <x:v>637</x:v>
       </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>638</x:v>
-      </x:c>
       <x:c r="H37" s="17">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I37" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J37" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M37" s="15" t="s">
         <x:v>25</x:v>
@@ -4089,13 +4116,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C38" s="15" t="s">
-        <x:v>639</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D38" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E38" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="F38" s="15" t="s">
         <x:v>640</x:v>
@@ -4104,19 +4131,19 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="H38" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J38" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M38" s="15" t="s">
         <x:v>25</x:v>
@@ -4133,28 +4160,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E39" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="F39" s="15" t="s">
-        <x:v>643</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="G39" s="15" t="s">
-        <x:v>644</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="H39" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J39" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M39" s="15" t="s">
         <x:v>25</x:v>
@@ -4165,34 +4192,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C40" s="15" t="s">
-        <x:v>645</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="D40" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E40" s="15" t="s">
-        <x:v>646</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="F40" s="15" t="s">
-        <x:v>647</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="G40" s="15" t="s">
-        <x:v>648</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="H40" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J40" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M40" s="15" t="s">
         <x:v>25</x:v>
@@ -4203,7 +4230,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C41" s="15" t="s">
-        <x:v>649</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="D41" s="16" t="s">
         <x:v>15</x:v>
@@ -4212,25 +4239,25 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="F41" s="15" t="s">
-        <x:v>650</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="G41" s="15" t="s">
-        <x:v>651</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="H41" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I41" s="18">
         <x:v>45824</x:v>
       </x:c>
       <x:c r="J41" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M41" s="15" t="s">
         <x:v>25</x:v>
@@ -4241,13 +4268,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C42" s="15" t="s">
-        <x:v>652</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="D42" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E42" s="15" t="s">
-        <x:v>653</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F42" s="15" t="s">
         <x:v>654</x:v>
@@ -4256,127 +4283,248 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="H42" s="17">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46115</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J42" s="16" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M42" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="21" t="s">
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I43" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K43" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L43" s="20">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I44" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K44" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L44" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="F45" s="15" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="G45" s="15" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="H45" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I45" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K45" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L45" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M45" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C45" s="22" t="s"/>
-      <x:c r="D45" s="22" t="s"/>
-      <x:c r="E45" s="23" t="s"/>
-      <x:c r="F45" s="23" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="24" t="s">
+      <x:c r="C48" s="22" t="s"/>
+      <x:c r="D48" s="22" t="s"/>
+      <x:c r="E48" s="23" t="s"/>
+      <x:c r="F48" s="23" t="s"/>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B49" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C46" s="25" t="s"/>
-      <x:c r="D46" s="25" t="s"/>
-      <x:c r="E46" s="25" t="s"/>
-      <x:c r="F46" s="26" t="s">
+      <x:c r="C49" s="25" t="s"/>
+      <x:c r="D49" s="25" t="s"/>
+      <x:c r="E49" s="25" t="s"/>
+      <x:c r="F49" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C47" s="28" t="s"/>
-      <x:c r="D47" s="28" t="s"/>
-      <x:c r="E47" s="28" t="s"/>
-      <x:c r="F47" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C48" s="28" t="s"/>
-      <x:c r="D48" s="28" t="s"/>
-      <x:c r="E48" s="28" t="s"/>
-      <x:c r="F48" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C50" s="28" t="s"/>
       <x:c r="D50" s="28" t="s"/>
       <x:c r="E50" s="28" t="s"/>
       <x:c r="F50" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C51" s="28" t="s"/>
       <x:c r="D51" s="28" t="s"/>
       <x:c r="E51" s="28" t="s"/>
       <x:c r="F51" s="29" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C52" s="28" t="s"/>
       <x:c r="D52" s="28" t="s"/>
       <x:c r="E52" s="28" t="s"/>
       <x:c r="F52" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="27" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="30" t="s">
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C53" s="31" t="s"/>
-      <x:c r="D53" s="31" t="s"/>
-      <x:c r="E53" s="31" t="s"/>
-      <x:c r="F53" s="32" t="n">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C57" s="31" t="s"/>
+      <x:c r="D57" s="31" t="s"/>
+      <x:c r="E57" s="31" t="s"/>
+      <x:c r="F57" s="32" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5314,18 +5462,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B48:F48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="667">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="675">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1118,7 +1118,7 @@
     <x:t>61-11-2025-1227</x:t>
   </x:si>
   <x:si>
-    <x:t>RUEL  BUGAS BALILI</x:t>
+    <x:t>RUEL BUGAS BALILI</x:t>
   </x:si>
   <x:si>
     <x:t>24-SROPPIX-16142</x:t>
@@ -1676,6 +1676,18 @@
     <x:t>61-3-2026-1384-689</x:t>
   </x:si>
   <x:si>
+    <x:t>DES APPLIANCE PLAZA INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESTIMO BLDG. POBLACION, BAYBAY, Liloy, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0620H-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1366-828</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
   </x:si>
   <x:si>
@@ -1688,6 +1700,18 @@
     <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
+    <x:t>PEARL'S ONLINE SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ariosa Street, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06359-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1357-656</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1958,7 +1982,7 @@
     <x:t>61-2-2026-1347-156</x:t>
   </x:si>
   <x:si>
-    <x:t>CHARLO F  SALUMAG</x:t>
+    <x:t>CHARLO F SALUMAG</x:t>
   </x:si>
   <x:si>
     <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
@@ -1970,7 +1994,7 @@
     <x:t>61-2-2026-1363-573</x:t>
   </x:si>
   <x:si>
-    <x:t>CLAUDIO  E. ELNAR</x:t>
+    <x:t>CLAUDIO E. ELNAR</x:t>
   </x:si>
   <x:si>
     <x:t>N/a N/A, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
@@ -3131,7 +3155,7 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="15" t="s">
-        <x:v>111</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
         <x:v>548</x:v>
@@ -3149,27 +3173,27 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46072.3153009259</x:v>
+        <x:v>46077.2833680556</x:v>
       </x:c>
       <x:c r="I12" s="18">
-        <x:v>46114</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216162</x:v>
+        <x:v>1217027</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.311412037</x:v>
+        <x:v>46094.1366782407</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
         <x:v>552</x:v>
@@ -3187,19 +3211,19 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46046.1343634259</x:v>
+        <x:v>46072.3153009259</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>45917</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216162</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46090.311412037</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>25</x:v>
@@ -3207,13 +3231,13 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
         <x:v>556</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
         <x:v>557</x:v>
@@ -3225,19 +3249,19 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>46021</x:v>
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46076.2633680556</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216188</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>5280</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46093.273287037</x:v>
+        <x:v>46094.1562731481</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3248,34 +3272,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>45991</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3286,34 +3310,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46024</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3324,7 +3348,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
@@ -3339,19 +3363,19 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>45883</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3377,19 +3401,19 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46076.318900463</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46074</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3397,7 +3421,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
         <x:v>575</x:v>
@@ -3415,19 +3439,19 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46058</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3435,37 +3459,37 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B20" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>575</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>579</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
-        <x:v>580</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>581</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46072.0333449074</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3476,34 +3500,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
-        <x:v>582</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="D21" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
-        <x:v>583</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F21" s="15" t="s">
-        <x:v>584</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>585</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>46071.1677662037</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I21" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216165</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46091.1948842593</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3514,7 +3538,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>586</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
@@ -3529,19 +3553,19 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3567,19 +3591,19 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I23" s="18">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3605,19 +3629,19 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
@@ -3628,34 +3652,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="15" t="s">
-        <x:v>594</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="D25" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="15" t="s">
-        <x:v>598</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="F25" s="15" t="s">
-        <x:v>599</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G25" s="15" t="s">
-        <x:v>600</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H25" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J25" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M25" s="15" t="s">
         <x:v>25</x:v>
@@ -3666,34 +3690,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C26" s="15" t="s">
-        <x:v>594</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D26" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="15" t="s">
-        <x:v>601</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F26" s="15" t="s">
-        <x:v>602</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="G26" s="15" t="s">
-        <x:v>603</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="H26" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I26" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M26" s="15" t="s">
         <x:v>25</x:v>
@@ -3704,34 +3728,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D27" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="15" t="s">
-        <x:v>605</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="F27" s="15" t="s">
-        <x:v>606</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="G27" s="15" t="s">
-        <x:v>607</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="H27" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I27" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M27" s="15" t="s">
         <x:v>25</x:v>
@@ -3742,34 +3766,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D28" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="15" t="s">
-        <x:v>608</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F28" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="G28" s="15" t="s">
-        <x:v>610</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="H28" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M28" s="15" t="s">
         <x:v>25</x:v>
@@ -3780,34 +3804,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C29" s="15" t="s">
-        <x:v>604</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="D29" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="15" t="s">
-        <x:v>601</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="F29" s="15" t="s">
-        <x:v>611</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="G29" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="H29" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J29" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M29" s="15" t="s">
         <x:v>25</x:v>
@@ -3818,34 +3842,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C30" s="15" t="s">
-        <x:v>604</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="D30" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="15" t="s">
-        <x:v>613</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F30" s="15" t="s">
-        <x:v>614</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="G30" s="15" t="s">
-        <x:v>615</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="H30" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M30" s="15" t="s">
         <x:v>25</x:v>
@@ -3856,34 +3880,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="15" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E31" s="15" t="s">
-        <x:v>601</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F31" s="15" t="s">
-        <x:v>617</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="G31" s="15" t="s">
-        <x:v>618</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="H31" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J31" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M31" s="15" t="s">
         <x:v>25</x:v>
@@ -3894,34 +3918,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C32" s="15" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="D32" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E32" s="15" t="s">
-        <x:v>619</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="F32" s="15" t="s">
-        <x:v>620</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="G32" s="15" t="s">
-        <x:v>621</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="H32" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I32" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J32" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M32" s="15" t="s">
         <x:v>25</x:v>
@@ -3932,34 +3956,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C33" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D33" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E33" s="15" t="s">
-        <x:v>622</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="F33" s="15" t="s">
-        <x:v>623</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="G33" s="15" t="s">
-        <x:v>624</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="H33" s="17">
-        <x:v>46079.0151851852</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>45602</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J33" s="16" t="n">
-        <x:v>1216174</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46093.1514351852</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M33" s="15" t="s">
         <x:v>25</x:v>
@@ -3970,34 +3994,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C34" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D34" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="F34" s="15" t="s">
-        <x:v>625</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G34" s="15" t="s">
-        <x:v>626</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="H34" s="17">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J34" s="16" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M34" s="15" t="s">
         <x:v>25</x:v>
@@ -4005,35 +4029,37 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C35" s="15" t="s">
-        <x:v>627</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s"/>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E35" s="15" t="s">
-        <x:v>628</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F35" s="15" t="s">
-        <x:v>629</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="G35" s="15" t="s">
-        <x:v>630</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="H35" s="17">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I35" s="17">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="s">
-        <x:v>630</x:v>
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I35" s="18">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M35" s="15" t="s">
         <x:v>25</x:v>
@@ -4041,14 +4067,16 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C36" s="15" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s"/>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E36" s="15" t="s">
-        <x:v>632</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F36" s="15" t="s">
         <x:v>633</x:v>
@@ -4057,19 +4085,19 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="H36" s="17">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I36" s="17">
-        <x:v>46090.2541203704</x:v>
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I36" s="18">
+        <x:v>45973</x:v>
       </x:c>
       <x:c r="J36" s="16" t="n">
-        <x:v>1216185</x:v>
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M36" s="15" t="s">
         <x:v>25</x:v>
@@ -4084,28 +4112,28 @@
       </x:c>
       <x:c r="D37" s="16" t="s"/>
       <x:c r="E37" s="15" t="s">
-        <x:v>632</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="F37" s="15" t="s">
-        <x:v>636</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="G37" s="15" t="s">
-        <x:v>637</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="H37" s="17">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I37" s="17">
-        <x:v>46090.2349305556</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1216187</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="s">
+        <x:v>638</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M37" s="15" t="s">
         <x:v>25</x:v>
@@ -4113,37 +4141,35 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C38" s="15" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s"/>
       <x:c r="E38" s="15" t="s">
-        <x:v>639</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="F38" s="15" t="s">
-        <x:v>640</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="G38" s="15" t="s">
-        <x:v>641</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="H38" s="17">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I38" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J38" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M38" s="15" t="s">
         <x:v>25</x:v>
@@ -4151,16 +4177,14 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="15" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s"/>
       <x:c r="E39" s="15" t="s">
-        <x:v>643</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="F39" s="15" t="s">
         <x:v>644</x:v>
@@ -4169,19 +4193,19 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="H39" s="17">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I39" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J39" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M39" s="15" t="s">
         <x:v>25</x:v>
@@ -4207,19 +4231,19 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="H40" s="17">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I40" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J40" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M40" s="15" t="s">
         <x:v>25</x:v>
@@ -4236,28 +4260,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E41" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="F41" s="15" t="s">
-        <x:v>651</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="G41" s="15" t="s">
-        <x:v>652</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="H41" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I41" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J41" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M41" s="15" t="s">
         <x:v>25</x:v>
@@ -4268,34 +4292,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C42" s="15" t="s">
-        <x:v>653</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="D42" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E42" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="F42" s="15" t="s">
-        <x:v>654</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="G42" s="15" t="s">
-        <x:v>655</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="H42" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I42" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J42" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M42" s="15" t="s">
         <x:v>25</x:v>
@@ -4306,34 +4330,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="15" t="s">
-        <x:v>656</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D43" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E43" s="15" t="s">
-        <x:v>657</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F43" s="15" t="s">
-        <x:v>658</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="G43" s="15" t="s">
-        <x:v>659</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="H43" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>45748</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J43" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M43" s="15" t="s">
         <x:v>25</x:v>
@@ -4344,34 +4368,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C44" s="15" t="s">
-        <x:v>660</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="D44" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E44" s="15" t="s">
-        <x:v>595</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F44" s="15" t="s">
-        <x:v>661</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="G44" s="15" t="s">
-        <x:v>662</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="H44" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>45824</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J44" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M44" s="15" t="s">
         <x:v>25</x:v>
@@ -4382,153 +4406,247 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C45" s="15" t="s">
-        <x:v>663</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="D45" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E45" s="15" t="s">
-        <x:v>664</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="F45" s="15" t="s">
-        <x:v>665</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="G45" s="15" t="s">
-        <x:v>666</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="H45" s="17">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J45" s="16" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M45" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="21" t="s">
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="F46" s="15" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="G46" s="15" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="H46" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I46" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K46" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L46" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M46" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="F47" s="15" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="G47" s="15" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="H47" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I47" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K47" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L47" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M47" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C48" s="22" t="s"/>
-      <x:c r="D48" s="22" t="s"/>
-      <x:c r="E48" s="23" t="s"/>
-      <x:c r="F48" s="23" t="s"/>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B49" s="24" t="s">
+      <x:c r="C50" s="22" t="s"/>
+      <x:c r="D50" s="22" t="s"/>
+      <x:c r="E50" s="23" t="s"/>
+      <x:c r="F50" s="23" t="s"/>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B51" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C49" s="25" t="s"/>
-      <x:c r="D49" s="25" t="s"/>
-      <x:c r="E49" s="25" t="s"/>
-      <x:c r="F49" s="26" t="s">
+      <x:c r="C51" s="25" t="s"/>
+      <x:c r="D51" s="25" t="s"/>
+      <x:c r="E51" s="25" t="s"/>
+      <x:c r="F51" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C50" s="28" t="s"/>
-      <x:c r="D50" s="28" t="s"/>
-      <x:c r="E50" s="28" t="s"/>
-      <x:c r="F50" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="27" t="s">
-        <x:v>111</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C52" s="28" t="s"/>
       <x:c r="D52" s="28" t="s"/>
       <x:c r="E52" s="28" t="s"/>
       <x:c r="F52" s="29" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
       <x:c r="B53" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C53" s="28" t="s"/>
       <x:c r="D53" s="28" t="s"/>
       <x:c r="E53" s="28" t="s"/>
       <x:c r="F53" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C54" s="28" t="s"/>
       <x:c r="D54" s="28" t="s"/>
       <x:c r="E54" s="28" t="s"/>
       <x:c r="F54" s="29" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
       <x:c r="B55" s="27" t="s">
-        <x:v>33</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C55" s="28" t="s"/>
       <x:c r="D55" s="28" t="s"/>
       <x:c r="E55" s="28" t="s"/>
       <x:c r="F55" s="29" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C56" s="28" t="s"/>
       <x:c r="D56" s="28" t="s"/>
       <x:c r="E56" s="28" t="s"/>
       <x:c r="F56" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C58" s="28" t="s"/>
+      <x:c r="D58" s="28" t="s"/>
+      <x:c r="E58" s="28" t="s"/>
+      <x:c r="F58" s="29" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="27" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C59" s="28" t="s"/>
+      <x:c r="D59" s="28" t="s"/>
+      <x:c r="E59" s="28" t="s"/>
+      <x:c r="F59" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B60" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C60" s="28" t="s"/>
+      <x:c r="D60" s="28" t="s"/>
+      <x:c r="E60" s="28" t="s"/>
+      <x:c r="F60" s="29" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="30" t="s">
+    <x:row r="61" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B61" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C57" s="31" t="s"/>
-      <x:c r="D57" s="31" t="s"/>
-      <x:c r="E57" s="31" t="s"/>
-      <x:c r="F57" s="32" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C61" s="31" t="s"/>
+      <x:c r="D61" s="31" t="s"/>
+      <x:c r="E61" s="31" t="s"/>
+      <x:c r="F61" s="32" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5462,12 +5580,10 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
+  <x:mergeCells count="14">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B48:F48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B50:F50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
@@ -5475,6 +5591,10 @@
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="675">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="694">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1700,6 +1700,18 @@
     <x:t>61-2-2026-1346-185</x:t>
   </x:si>
   <x:si>
+    <x:t>HIGH-SPEED MOTORCYCLE PARTS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok Pines 2, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06354-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1355-880</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEARL'S ONLINE SHOP</x:t>
   </x:si>
   <x:si>
@@ -1712,6 +1724,18 @@
     <x:t>61-2-2026-1357-656</x:t>
   </x:si>
   <x:si>
+    <x:t>SLIM BX ELECTRONICS AND TELECOMMUNICATION PARTS AND EQUIPMENT RETAILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vicencio Sagun Street, Brgy San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06389-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1360-023</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1838,6 +1862,15 @@
     <x:t>61-2-2026-1352-743</x:t>
   </x:si>
   <x:si>
+    <x:t>PRK. KAMANGGAHAN, CURVADA, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1006-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1337-307</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -2055,6 +2088,30 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1361-291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODEL PALMERO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 4, GUIPOS, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17SROPIX11062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1336-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROMEO CAPANGPANGAN DUMAOG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NA GUMAMELA, SAN CARLOS, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22-SROPIX-13860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1390-540</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3249,19 +3306,19 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46076.2633564815</x:v>
+        <x:v>46076.245</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>46076.2633680556</x:v>
+        <x:v>46076.2450115741</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216188</x:v>
+        <x:v>1216190</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>4530</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46094.1562731481</x:v>
+        <x:v>46094.1710416667</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>25</x:v>
@@ -3269,13 +3326,13 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
         <x:v>560</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
         <x:v>561</x:v>
@@ -3287,19 +3344,19 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>45917</x:v>
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46076.2633680556</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216188</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46094.1562731481</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>25</x:v>
@@ -3307,13 +3364,13 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
         <x:v>564</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
         <x:v>565</x:v>
@@ -3325,19 +3382,19 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>46021</x:v>
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46076.3755439815</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216189</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>5280</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46093.273287037</x:v>
+        <x:v>46094.1653935185</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>25</x:v>
@@ -3348,34 +3405,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>568</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>570</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>45991</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>25</x:v>
@@ -3386,34 +3443,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>571</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>572</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>573</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>574</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46024</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3424,7 +3481,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
@@ -3439,19 +3496,19 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>45883</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3477,19 +3534,19 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46076.318900463</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46074</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>
@@ -3497,7 +3554,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B21" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="15" t="s">
         <x:v>583</x:v>
@@ -3515,19 +3572,19 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>46058</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -3535,37 +3592,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C22" s="15" t="s">
-        <x:v>583</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D22" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="15" t="s">
-        <x:v>587</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F22" s="15" t="s">
-        <x:v>588</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>589</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>46072.0333449074</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1216156</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46090.2584837963</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -3576,34 +3633,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C23" s="15" t="s">
-        <x:v>590</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="D23" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="15" t="s">
-        <x:v>591</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F23" s="15" t="s">
-        <x:v>592</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="G23" s="15" t="s">
-        <x:v>593</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="H23" s="17">
-        <x:v>46071.1677662037</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I23" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J23" s="16" t="n">
-        <x:v>1216165</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K23" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="20">
-        <x:v>46091.1948842593</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M23" s="15" t="s">
         <x:v>25</x:v>
@@ -3614,7 +3671,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="15" t="s">
-        <x:v>594</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="D24" s="16" t="s">
         <x:v>15</x:v>
@@ -3629,19 +3686,19 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="H24" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M24" s="15" t="s">
         <x:v>25</x:v>
@@ -3667,19 +3724,19 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="H25" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J25" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M25" s="15" t="s">
         <x:v>25</x:v>
@@ -3705,19 +3762,19 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="H26" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M26" s="15" t="s">
         <x:v>25</x:v>
@@ -3728,34 +3785,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C27" s="15" t="s">
-        <x:v>602</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="D27" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="15" t="s">
-        <x:v>606</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F27" s="15" t="s">
-        <x:v>607</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="G27" s="15" t="s">
-        <x:v>608</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="H27" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M27" s="15" t="s">
         <x:v>25</x:v>
@@ -3766,34 +3823,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C28" s="15" t="s">
-        <x:v>602</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="D28" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F28" s="15" t="s">
-        <x:v>610</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="G28" s="15" t="s">
-        <x:v>611</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="H28" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46071.3305671296</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46058</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216193</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46094.1906365741</x:v>
       </x:c>
       <x:c r="M28" s="15" t="s">
         <x:v>25</x:v>
@@ -3804,34 +3861,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C29" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D29" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="15" t="s">
-        <x:v>613</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F29" s="15" t="s">
-        <x:v>614</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="G29" s="15" t="s">
-        <x:v>615</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="H29" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I29" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J29" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M29" s="15" t="s">
         <x:v>25</x:v>
@@ -3842,34 +3899,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C30" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D30" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="15" t="s">
-        <x:v>616</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F30" s="15" t="s">
-        <x:v>617</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="G30" s="15" t="s">
-        <x:v>618</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="H30" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I30" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M30" s="15" t="s">
         <x:v>25</x:v>
@@ -3880,34 +3937,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E31" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F31" s="15" t="s">
-        <x:v>619</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="G31" s="15" t="s">
-        <x:v>620</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="H31" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I31" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M31" s="15" t="s">
         <x:v>25</x:v>
@@ -3918,34 +3975,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C32" s="15" t="s">
-        <x:v>612</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D32" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E32" s="15" t="s">
-        <x:v>621</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="F32" s="15" t="s">
-        <x:v>622</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="G32" s="15" t="s">
-        <x:v>623</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="H32" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I32" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J32" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M32" s="15" t="s">
         <x:v>25</x:v>
@@ -3956,34 +4013,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C33" s="15" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D33" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E33" s="15" t="s">
-        <x:v>609</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="F33" s="15" t="s">
-        <x:v>625</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G33" s="15" t="s">
-        <x:v>626</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="H33" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J33" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M33" s="15" t="s">
         <x:v>25</x:v>
@@ -3994,34 +4051,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C34" s="15" t="s">
-        <x:v>624</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D34" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="15" t="s">
-        <x:v>627</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F34" s="15" t="s">
-        <x:v>628</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="G34" s="15" t="s">
-        <x:v>629</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="H34" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J34" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M34" s="15" t="s">
         <x:v>25</x:v>
@@ -4032,34 +4089,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C35" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D35" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E35" s="15" t="s">
-        <x:v>630</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="F35" s="15" t="s">
-        <x:v>631</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="G35" s="15" t="s">
-        <x:v>632</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="H35" s="17">
-        <x:v>46079.0151851852</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>45602</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J35" s="16" t="n">
-        <x:v>1216174</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46093.1514351852</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M35" s="15" t="s">
         <x:v>25</x:v>
@@ -4070,34 +4127,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C36" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="D36" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E36" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F36" s="15" t="s">
-        <x:v>633</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="G36" s="15" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="H36" s="17">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I36" s="18">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J36" s="16" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M36" s="15" t="s">
         <x:v>25</x:v>
@@ -4105,35 +4162,37 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C37" s="15" t="s">
         <x:v>635</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="s"/>
+      <x:c r="D37" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E37" s="15" t="s">
-        <x:v>636</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="F37" s="15" t="s">
-        <x:v>637</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="G37" s="15" t="s">
-        <x:v>638</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H37" s="17">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="s">
-        <x:v>638</x:v>
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I37" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M37" s="15" t="s">
         <x:v>25</x:v>
@@ -4141,35 +4200,37 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C38" s="15" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s"/>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E38" s="15" t="s">
-        <x:v>640</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="F38" s="15" t="s">
-        <x:v>641</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="G38" s="15" t="s">
-        <x:v>642</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="H38" s="17">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I38" s="17">
-        <x:v>46090.2541203704</x:v>
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I38" s="18">
+        <x:v>45602</x:v>
       </x:c>
       <x:c r="J38" s="16" t="n">
-        <x:v>1216185</x:v>
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M38" s="15" t="s">
         <x:v>25</x:v>
@@ -4177,14 +4238,16 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C39" s="15" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s"/>
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E39" s="15" t="s">
-        <x:v>640</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F39" s="15" t="s">
         <x:v>644</x:v>
@@ -4193,19 +4256,19 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="H39" s="17">
-        <x:v>46090.2349189815</x:v>
-      </x:c>
-      <x:c r="I39" s="17">
-        <x:v>46090.2349305556</x:v>
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I39" s="18">
+        <x:v>45973</x:v>
       </x:c>
       <x:c r="J39" s="16" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M39" s="15" t="s">
         <x:v>25</x:v>
@@ -4213,14 +4276,12 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B40" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="15" t="s">
         <x:v>646</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D40" s="16" t="s"/>
       <x:c r="E40" s="15" t="s">
         <x:v>647</x:v>
       </x:c>
@@ -4231,19 +4292,19 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="H40" s="17">
-        <x:v>46073.0262847222</x:v>
-      </x:c>
-      <x:c r="I40" s="18">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1216157</x:v>
+        <x:v>46090.2854050926</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="s">
+        <x:v>649</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M40" s="15" t="s">
         <x:v>25</x:v>
@@ -4251,14 +4312,12 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="15" t="s">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D41" s="16" t="s"/>
       <x:c r="E41" s="15" t="s">
         <x:v>651</x:v>
       </x:c>
@@ -4269,19 +4328,19 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="H41" s="17">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I41" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I41" s="17">
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J41" s="16" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M41" s="15" t="s">
         <x:v>25</x:v>
@@ -4289,37 +4348,35 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="15" t="s">
         <x:v>654</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D42" s="16" t="s"/>
       <x:c r="E42" s="15" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
         <x:v>655</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="s">
+      <x:c r="G42" s="15" t="s">
         <x:v>656</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="s">
-        <x:v>657</x:v>
-      </x:c>
       <x:c r="H42" s="17">
-        <x:v>46073.0478472222</x:v>
-      </x:c>
-      <x:c r="I42" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I42" s="17">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J42" s="16" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M42" s="15" t="s">
         <x:v>25</x:v>
@@ -4330,13 +4387,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="15" t="s">
-        <x:v>658</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="D43" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E43" s="15" t="s">
-        <x:v>603</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="F43" s="15" t="s">
         <x:v>659</x:v>
@@ -4345,19 +4402,19 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="H43" s="17">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I43" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J43" s="16" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M43" s="15" t="s">
         <x:v>25</x:v>
@@ -4374,28 +4431,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E44" s="15" t="s">
-        <x:v>603</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="F44" s="15" t="s">
-        <x:v>662</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="G44" s="15" t="s">
-        <x:v>663</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="H44" s="17">
-        <x:v>46073.061099537</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>46036</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J44" s="16" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M44" s="15" t="s">
         <x:v>25</x:v>
@@ -4406,34 +4463,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C45" s="15" t="s">
-        <x:v>664</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="D45" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E45" s="15" t="s">
-        <x:v>665</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="F45" s="15" t="s">
-        <x:v>666</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="G45" s="15" t="s">
-        <x:v>667</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="H45" s="17">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J45" s="16" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M45" s="15" t="s">
         <x:v>25</x:v>
@@ -4444,34 +4501,34 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C46" s="15" t="s">
-        <x:v>668</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="D46" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="15" t="s">
-        <x:v>603</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F46" s="15" t="s">
-        <x:v>669</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="G46" s="15" t="s">
-        <x:v>670</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="H46" s="17">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I46" s="18">
         <x:v>45824</x:v>
       </x:c>
       <x:c r="J46" s="16" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M46" s="15" t="s">
         <x:v>25</x:v>
@@ -4482,13 +4539,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C47" s="15" t="s">
-        <x:v>671</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="D47" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E47" s="15" t="s">
-        <x:v>672</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="F47" s="15" t="s">
         <x:v>673</x:v>
@@ -4497,161 +4554,346 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="H47" s="17">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46115</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J47" s="16" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M47" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="21" t="s">
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="F48" s="15" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="G48" s="15" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="H48" s="17">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I48" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K48" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L48" s="20">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M48" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C49" s="15" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E49" s="15" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="F49" s="15" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="G49" s="15" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="H49" s="17">
+        <x:v>46073.0763541667</x:v>
+      </x:c>
+      <x:c r="I49" s="18">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J49" s="16" t="n">
+        <x:v>1216149</x:v>
+      </x:c>
+      <x:c r="K49" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L49" s="20">
+        <x:v>46090.2162847222</x:v>
+      </x:c>
+      <x:c r="M49" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C50" s="15" t="s">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E50" s="15" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="F50" s="15" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="G50" s="15" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="H50" s="17">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I50" s="18">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J50" s="16" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K50" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L50" s="20">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M50" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B51" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C51" s="15" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E51" s="15" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="F51" s="15" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="G51" s="15" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="H51" s="17">
+        <x:v>46071.2853587963</x:v>
+      </x:c>
+      <x:c r="I51" s="18">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J51" s="16" t="n">
+        <x:v>1216191</x:v>
+      </x:c>
+      <x:c r="K51" s="19" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L51" s="20">
+        <x:v>46094.1777199074</x:v>
+      </x:c>
+      <x:c r="M51" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B52" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C52" s="15" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E52" s="15" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="F52" s="15" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="G52" s="15" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="H52" s="17">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I52" s="18">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J52" s="16" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K52" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L52" s="20">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M52" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="21" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C50" s="22" t="s"/>
-      <x:c r="D50" s="22" t="s"/>
-      <x:c r="E50" s="23" t="s"/>
-      <x:c r="F50" s="23" t="s"/>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B51" s="24" t="s">
+      <x:c r="C55" s="22" t="s"/>
+      <x:c r="D55" s="22" t="s"/>
+      <x:c r="E55" s="23" t="s"/>
+      <x:c r="F55" s="23" t="s"/>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B56" s="24" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C51" s="25" t="s"/>
-      <x:c r="D51" s="25" t="s"/>
-      <x:c r="E51" s="25" t="s"/>
-      <x:c r="F51" s="26" t="s">
+      <x:c r="C56" s="25" t="s"/>
+      <x:c r="D56" s="25" t="s"/>
+      <x:c r="E56" s="25" t="s"/>
+      <x:c r="F56" s="26" t="s">
         <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C52" s="28" t="s"/>
-      <x:c r="D52" s="28" t="s"/>
-      <x:c r="E52" s="28" t="s"/>
-      <x:c r="F52" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C57" s="28" t="s"/>
       <x:c r="D57" s="28" t="s"/>
       <x:c r="E57" s="28" t="s"/>
       <x:c r="F57" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C58" s="28" t="s"/>
       <x:c r="D58" s="28" t="s"/>
       <x:c r="E58" s="28" t="s"/>
       <x:c r="F58" s="29" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="27" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C59" s="28" t="s"/>
       <x:c r="D59" s="28" t="s"/>
       <x:c r="E59" s="28" t="s"/>
       <x:c r="F59" s="29" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="18" customHeight="1">
       <x:c r="B60" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C60" s="28" t="s"/>
       <x:c r="D60" s="28" t="s"/>
       <x:c r="E60" s="28" t="s"/>
       <x:c r="F60" s="29" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B61" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B61" s="27" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C61" s="28" t="s"/>
+      <x:c r="D61" s="28" t="s"/>
+      <x:c r="E61" s="28" t="s"/>
+      <x:c r="F61" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B62" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C62" s="28" t="s"/>
+      <x:c r="D62" s="28" t="s"/>
+      <x:c r="E62" s="28" t="s"/>
+      <x:c r="F62" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B63" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C63" s="28" t="s"/>
+      <x:c r="D63" s="28" t="s"/>
+      <x:c r="E63" s="28" t="s"/>
+      <x:c r="F63" s="29" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B64" s="27" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C64" s="28" t="s"/>
+      <x:c r="D64" s="28" t="s"/>
+      <x:c r="E64" s="28" t="s"/>
+      <x:c r="F64" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B65" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C65" s="28" t="s"/>
+      <x:c r="D65" s="28" t="s"/>
+      <x:c r="E65" s="28" t="s"/>
+      <x:c r="F65" s="29" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B66" s="30" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C61" s="31" t="s"/>
-      <x:c r="D61" s="31" t="s"/>
-      <x:c r="E61" s="31" t="s"/>
-      <x:c r="F61" s="32" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C66" s="31" t="s"/>
+      <x:c r="D66" s="31" t="s"/>
+      <x:c r="E66" s="31" t="s"/>
+      <x:c r="F66" s="32" t="n">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
     <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5583,18 +5825,18 @@
   <x:mergeCells count="14">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B50:F50"/>
-    <x:mergeCell ref="B51:E51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
-    <x:mergeCell ref="B54:E54"/>
-    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B55:F55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
     <x:mergeCell ref="B61:E61"/>
+    <x:mergeCell ref="B62:E62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -287,6 +287,42 @@
     <x:t>61-8-2025-1088</x:t>
   </x:si>
   <x:si>
+    <x:t>Radio Station License (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RSL-ROIX-01116-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GODOFREDO M. LIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zone II, La Purisima, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RPTR-II-00018-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THUNDER BRAVO NETWORK, INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lanote Bliss, City Of Isabela, City Of Isabela</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FB-II-00041-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1140</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radio Station License - WDN (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -302,42 +338,6 @@
     <x:t>61-8-2025-1114</x:t>
   </x:si>
   <x:si>
-    <x:t>Radio Station License (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RSL-ROIX-01116-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radio Station License (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GODOFREDO M. LIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zone II, La Purisima, Zamboanga City, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RPTR-II-00018-01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THUNDER BRAVO NETWORK, INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lanote Bliss, City Of Isabela, City Of Isabela</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FB-II-00041-19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1140</x:t>
-  </x:si>
-  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
   </x:si>
   <x:si>
@@ -377,18 +377,18 @@
     <x:t>61-8-2025-1135</x:t>
   </x:si>
   <x:si>
+    <x:t>MP-ROIX-01007-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1093</x:t>
+  </x:si>
+  <x:si>
     <x:t>MP-ROIX-01008-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-8-2025-1095</x:t>
   </x:si>
   <x:si>
-    <x:t>MP-ROIX-01007-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1093</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -1535,27 +1535,27 @@
     <x:t>PUROK KAMANGGAHAN, CURVADA, Tukuran, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
+    <x:t>MS9/FV-0860-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1311-296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamanggahan, Curvada, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0979-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1310-247</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-0866-18</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1312-079</x:t>
   </x:si>
   <x:si>
-    <x:t>MS9/FV-0860-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1311-296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kamanggahan, Curvada, Tukuran, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0979-19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1310-247</x:t>
-  </x:si>
-  <x:si>
     <x:t>REX M. ALBAÑO</x:t>
   </x:si>
   <x:si>
@@ -1751,6 +1751,15 @@
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
     <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1760,15 +1769,6 @@
     <x:t>61-1-2026-1293-860</x:t>
   </x:si>
   <x:si>
-    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRR-110615E-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1292-941</x:t>
-  </x:si>
-  <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1883,6 +1883,15 @@
     <x:t>61-2-2026-1364-213</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/a Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1892,18 +1901,27 @@
     <x:t>61-2-2026-1344-597</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0880-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1343-619</x:t>
-  </x:si>
-  <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0881-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1342-435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1077-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1367-348</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1913,28 +1931,10 @@
     <x:t>61-2-2026-1369-049</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-1077-20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1367-348</x:t>
-  </x:si>
-  <x:si>
     <x:t>MS-4878-23</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1362-288</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0881-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1342-435</x:t>
   </x:si>
   <x:si>
     <x:t>REY S. BURBURAN</x:t>
@@ -3458,19 +3458,19 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46021</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -3496,19 +3496,19 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -3914,19 +3914,19 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="H30" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I30" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K30" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L30" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M30" s="15" t="s">
         <x:v>25</x:v>
@@ -3952,19 +3952,19 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="H31" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I31" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M31" s="15" t="s">
         <x:v>25</x:v>
@@ -3990,19 +3990,19 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="H32" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I32" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J32" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M32" s="15" t="s">
         <x:v>25</x:v>
@@ -4057,28 +4057,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="15" t="s">
-        <x:v>620</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F34" s="15" t="s">
-        <x:v>630</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="G34" s="15" t="s">
-        <x:v>631</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="H34" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J34" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M34" s="15" t="s">
         <x:v>25</x:v>
@@ -4095,7 +4095,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E35" s="15" t="s">
-        <x:v>632</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F35" s="15" t="s">
         <x:v>633</x:v>
@@ -4104,19 +4104,19 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="H35" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J35" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M35" s="15" t="s">
         <x:v>25</x:v>
@@ -4133,7 +4133,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E36" s="15" t="s">
-        <x:v>620</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F36" s="15" t="s">
         <x:v>636</x:v>
@@ -7765,51 +7765,51 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="H14" s="17">
-        <x:v>45881.3064236111</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>45871</x:v>
+        <x:v>45882.0658796296</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45882.0658912037</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1195693</x:v>
+        <x:v>1195701</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
-        <x:v>4275</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>45897.0449189815</x:v>
+        <x:v>45883.2549537037</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
         <x:v>91</x:v>
@@ -7818,57 +7818,57 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45882.0658912037</x:v>
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>45885</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1195701</x:v>
+        <x:v>1346453</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
-        <x:v>2496</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>45883.2549537037</x:v>
+        <x:v>45881.0887037037</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="G16" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="H16" s="17">
-        <x:v>45881.0630902778</x:v>
+        <x:v>45897.2535648148</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>45885</x:v>
+        <x:v>45847</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1346453</x:v>
+        <x:v>1346494</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>45881.0887037037</x:v>
+        <x:v>45897.2982407407</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -7876,7 +7876,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="15" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
         <x:v>98</x:v>
@@ -7894,19 +7894,19 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>45897.2535648148</x:v>
+        <x:v>45881.3064236111</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>45847</x:v>
+        <x:v>45871</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1346494</x:v>
+        <x:v>1195693</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
-        <x:v>2490</x:v>
+        <x:v>4275</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>45897.2982407407</x:v>
+        <x:v>45897.0449189815</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
@@ -8046,19 +8046,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>45875.361724537</x:v>
+        <x:v>45875.2324652778</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>45921</x:v>
+        <x:v>45903</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1215851</x:v>
+        <x:v>1215852</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>45876.2230902778</x:v>
+        <x:v>45876.2319791667</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>25</x:v>
@@ -8084,19 +8084,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H22" s="17">
-        <x:v>45875.2324652778</x:v>
+        <x:v>45875.361724537</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>45903</x:v>
+        <x:v>45921</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>1215852</x:v>
+        <x:v>1215851</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>45876.2319791667</x:v>
+        <x:v>45876.2230902778</x:v>
       </x:c>
       <x:c r="M22" s="15" t="s">
         <x:v>25</x:v>
@@ -8637,7 +8637,7 @@
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
       <x:c r="B44" s="27" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C44" s="28" t="s"/>
       <x:c r="D44" s="28" t="s"/>
@@ -8648,7 +8648,7 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
       <x:c r="B45" s="27" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C45" s="28" t="s"/>
       <x:c r="D45" s="28" t="s"/>
@@ -8659,7 +8659,7 @@
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C46" s="28" t="s"/>
       <x:c r="D46" s="28" t="s"/>
@@ -10049,7 +10049,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
         <x:v>185</x:v>
@@ -10710,7 +10710,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="27" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="28" t="s"/>
       <x:c r="D33" s="28" t="s"/>
@@ -19474,19 +19474,19 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46057.2800462963</x:v>
+        <x:v>46057.272025463</x:v>
       </x:c>
       <x:c r="I18" s="18">
-        <x:v>46052</x:v>
+        <x:v>46045</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216117</x:v>
+        <x:v>1216121</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
-        <x:v>2010</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46065.2796412037</x:v>
+        <x:v>46065.2951388889</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>25</x:v>
@@ -19503,28 +19503,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>500</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
-        <x:v>503</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>504</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46057.272025463</x:v>
+        <x:v>46057.2657523148</x:v>
       </x:c>
       <x:c r="I19" s="18">
-        <x:v>46045</x:v>
+        <x:v>46039</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216121</x:v>
+        <x:v>1216119</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46065.2951388889</x:v>
+        <x:v>46065.285474537</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>25</x:v>
@@ -19541,7 +19541,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>505</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F20" s="15" t="s">
         <x:v>506</x:v>
@@ -19550,19 +19550,19 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46057.2657523148</x:v>
+        <x:v>46057.2800462963</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>46039</x:v>
+        <x:v>46052</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216119</x:v>
+        <x:v>1216117</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46065.285474537</x:v>
+        <x:v>46065.2796412037</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>25</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -2993,7 +2993,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3063,7 +3063,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>
@@ -6177,7 +6177,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6247,7 +6247,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
@@ -7634,7 +7634,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -7704,7 +7704,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>
@@ -10074,7 +10074,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -10144,7 +10144,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>
@@ -12115,7 +12115,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -12185,7 +12185,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -13701,7 +13701,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -13769,7 +13769,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>
@@ -15801,7 +15801,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -15871,7 +15871,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -17408,7 +17408,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -17476,7 +17476,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>
@@ -19192,7 +19192,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -19262,7 +19262,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>40</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="718">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1787,6 +1787,18 @@
     <x:t>61-2-2026-1360-023</x:t>
   </x:si>
   <x:si>
+    <x:t>3D'S&amp;B CELLPHONE AND ACCESORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gumahan, Poblacion, Josefina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09073370000-0052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1377-766</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1802,6 +1814,15 @@
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
+    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-110613A-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1293-860</x:t>
+  </x:si>
+  <x:si>
     <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1811,15 +1832,6 @@
     <x:t>61-1-2026-1292-941</x:t>
   </x:si>
   <x:si>
-    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-110613A-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1293-860</x:t>
-  </x:si>
-  <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1880,6 +1892,15 @@
     <x:t>AL S. BURBURAN</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0877-18(ren)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1340-327</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/a Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1887,15 +1908,6 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1354-796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0877-18(ren)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1340-327</x:t>
   </x:si>
   <x:si>
     <x:t>FEY S. BURBURAN</x:t>
@@ -3588,19 +3600,19 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="H21" s="18">
-        <x:v>46046.1343634259</x:v>
+        <x:v>46083.2965972222</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J21" s="17" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216198</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46098.2996296296</x:v>
       </x:c>
       <x:c r="M21" s="16" t="s">
         <x:v>26</x:v>
@@ -3626,19 +3638,19 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="H22" s="18">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I22" s="18">
-        <x:v>45991</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J22" s="17" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K22" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="20">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M22" s="16" t="s">
         <x:v>26</x:v>
@@ -3649,19 +3661,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>589</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D23" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="16" t="s">
-        <x:v>593</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F23" s="16" t="s">
-        <x:v>594</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="G23" s="16" t="s">
-        <x:v>595</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="H23" s="18">
         <x:v>46046.1309027778</x:v>
@@ -3687,7 +3699,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
-        <x:v>596</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D24" s="17" t="s">
         <x:v>16</x:v>
@@ -3702,19 +3714,19 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="H24" s="18">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I24" s="18">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J24" s="17" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K24" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="20">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M24" s="16" t="s">
         <x:v>26</x:v>
@@ -3740,19 +3752,19 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="H25" s="18">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I25" s="18">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J25" s="17" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K25" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="20">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M25" s="16" t="s">
         <x:v>26</x:v>
@@ -3778,19 +3790,19 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="H26" s="18">
-        <x:v>46076.318900463</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I26" s="18">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J26" s="17" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K26" s="19" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="20">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M26" s="16" t="s">
         <x:v>26</x:v>
@@ -3798,13 +3810,13 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="C27" s="16" t="s">
-        <x:v>565</x:v>
-      </x:c>
       <x:c r="D27" s="17" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="16" t="s">
         <x:v>609</x:v>
@@ -3816,19 +3828,19 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="H27" s="18">
-        <x:v>46079.2852546296</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I27" s="18">
-        <x:v>46079.2852662037</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J27" s="17" t="n">
-        <x:v>1216195</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K27" s="19" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="20">
-        <x:v>46097.2459143518</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M27" s="16" t="s">
         <x:v>26</x:v>
@@ -3836,37 +3848,37 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B28" s="16" t="s">
-        <x:v>608</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C28" s="16" t="s">
-        <x:v>573</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D28" s="17" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="16" t="s">
-        <x:v>612</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="F28" s="16" t="s">
-        <x:v>613</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="G28" s="16" t="s">
-        <x:v>614</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="H28" s="18">
-        <x:v>46079.2747222222</x:v>
+        <x:v>46079.2852546296</x:v>
       </x:c>
       <x:c r="I28" s="18">
-        <x:v>46079.2747453704</x:v>
+        <x:v>46079.2852662037</x:v>
       </x:c>
       <x:c r="J28" s="17" t="n">
-        <x:v>1216196</x:v>
+        <x:v>1216195</x:v>
       </x:c>
       <x:c r="K28" s="19" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L28" s="20">
-        <x:v>46097.2536342593</x:v>
+        <x:v>46097.2459143518</x:v>
       </x:c>
       <x:c r="M28" s="16" t="s">
         <x:v>26</x:v>
@@ -3874,13 +3886,13 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="16" t="s">
-        <x:v>21</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C29" s="16" t="s">
-        <x:v>615</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="D29" s="17" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="16" t="s">
         <x:v>616</x:v>
@@ -3892,19 +3904,19 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="H29" s="18">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46079.2747222222</x:v>
       </x:c>
       <x:c r="I29" s="18">
-        <x:v>46058</x:v>
+        <x:v>46079.2747453704</x:v>
       </x:c>
       <x:c r="J29" s="17" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216196</x:v>
       </x:c>
       <x:c r="K29" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L29" s="20">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46097.2536342593</x:v>
       </x:c>
       <x:c r="M29" s="16" t="s">
         <x:v>26</x:v>
@@ -3915,19 +3927,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C30" s="16" t="s">
-        <x:v>615</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D30" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="16" t="s">
-        <x:v>619</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F30" s="16" t="s">
-        <x:v>620</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="G30" s="16" t="s">
-        <x:v>621</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="H30" s="18">
         <x:v>46072.0333449074</x:v>
@@ -3953,7 +3965,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="16" t="s">
-        <x:v>622</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="D31" s="17" t="s">
         <x:v>16</x:v>
@@ -3968,19 +3980,19 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="H31" s="18">
-        <x:v>46071.1677662037</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I31" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="17" t="n">
-        <x:v>1216165</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K31" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="20">
-        <x:v>46091.1948842593</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M31" s="16" t="s">
         <x:v>26</x:v>
@@ -4006,19 +4018,19 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="H32" s="18">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I32" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J32" s="17" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K32" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M32" s="16" t="s">
         <x:v>26</x:v>
@@ -4044,19 +4056,19 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="H33" s="18">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I33" s="18">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J33" s="17" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K33" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L33" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M33" s="16" t="s">
         <x:v>26</x:v>
@@ -4067,34 +4079,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="16" t="s">
-        <x:v>507</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D34" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="16" t="s">
-        <x:v>634</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="F34" s="16" t="s">
-        <x:v>635</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="G34" s="16" t="s">
-        <x:v>636</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="H34" s="18">
-        <x:v>46071.3305671296</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I34" s="18">
-        <x:v>46112</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J34" s="17" t="n">
-        <x:v>1216193</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K34" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L34" s="20">
-        <x:v>46094.1906365741</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M34" s="16" t="s">
         <x:v>26</x:v>
@@ -4105,7 +4117,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C35" s="16" t="s">
-        <x:v>637</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D35" s="17" t="s">
         <x:v>16</x:v>
@@ -4120,19 +4132,19 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="H35" s="18">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46071.3305671296</x:v>
       </x:c>
       <x:c r="I35" s="18">
-        <x:v>46058</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J35" s="17" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216193</x:v>
       </x:c>
       <x:c r="K35" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L35" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46094.1906365741</x:v>
       </x:c>
       <x:c r="M35" s="16" t="s">
         <x:v>26</x:v>
@@ -4143,34 +4155,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C36" s="16" t="s">
-        <x:v>637</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D36" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="16" t="s">
-        <x:v>641</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F36" s="16" t="s">
-        <x:v>642</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="G36" s="16" t="s">
-        <x:v>643</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="H36" s="18">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I36" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J36" s="17" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K36" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L36" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M36" s="16" t="s">
         <x:v>26</x:v>
@@ -4181,34 +4193,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C37" s="16" t="s">
-        <x:v>637</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D37" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="16" t="s">
-        <x:v>644</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F37" s="16" t="s">
-        <x:v>645</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="G37" s="16" t="s">
-        <x:v>646</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="H37" s="18">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I37" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J37" s="17" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K37" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L37" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M37" s="16" t="s">
         <x:v>26</x:v>
@@ -4219,34 +4231,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C38" s="16" t="s">
-        <x:v>647</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D38" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="16" t="s">
-        <x:v>638</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="F38" s="16" t="s">
-        <x:v>648</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G38" s="16" t="s">
-        <x:v>649</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="H38" s="18">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I38" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J38" s="17" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K38" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L38" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M38" s="16" t="s">
         <x:v>26</x:v>
@@ -4257,34 +4269,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C39" s="16" t="s">
-        <x:v>647</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D39" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="16" t="s">
-        <x:v>650</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F39" s="16" t="s">
-        <x:v>651</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="G39" s="16" t="s">
-        <x:v>652</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="H39" s="18">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I39" s="18">
-        <x:v>46030</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J39" s="17" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K39" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L39" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M39" s="16" t="s">
         <x:v>26</x:v>
@@ -4295,34 +4307,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>647</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D40" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="16" t="s">
-        <x:v>653</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="F40" s="16" t="s">
-        <x:v>654</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="G40" s="16" t="s">
-        <x:v>655</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="H40" s="18">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I40" s="18">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J40" s="17" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K40" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L40" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M40" s="16" t="s">
         <x:v>26</x:v>
@@ -4333,34 +4345,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="16" t="s">
-        <x:v>647</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D41" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="16" t="s">
-        <x:v>656</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="F41" s="16" t="s">
-        <x:v>657</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="G41" s="16" t="s">
-        <x:v>658</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="H41" s="18">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I41" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J41" s="17" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K41" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L41" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M41" s="16" t="s">
         <x:v>26</x:v>
@@ -4371,7 +4383,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C42" s="16" t="s">
-        <x:v>659</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D42" s="17" t="s">
         <x:v>16</x:v>
@@ -4386,19 +4398,19 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="H42" s="18">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I42" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J42" s="17" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K42" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L42" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M42" s="16" t="s">
         <x:v>26</x:v>
@@ -4409,34 +4421,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>659</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="D43" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="16" t="s">
-        <x:v>638</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="F43" s="16" t="s">
-        <x:v>663</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="G43" s="16" t="s">
-        <x:v>664</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="H43" s="18">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I43" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J43" s="17" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K43" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L43" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M43" s="16" t="s">
         <x:v>26</x:v>
@@ -4447,34 +4459,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C44" s="16" t="s">
-        <x:v>265</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="D44" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="16" t="s">
-        <x:v>266</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F44" s="16" t="s">
-        <x:v>665</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="G44" s="16" t="s">
-        <x:v>666</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="H44" s="18">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I44" s="18">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J44" s="17" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K44" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L44" s="20">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M44" s="16" t="s">
         <x:v>26</x:v>
@@ -4491,28 +4503,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="16" t="s">
-        <x:v>667</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F45" s="16" t="s">
-        <x:v>668</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="G45" s="16" t="s">
-        <x:v>669</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="H45" s="18">
-        <x:v>46079.0151851852</x:v>
+        <x:v>45988.1893402778</x:v>
       </x:c>
       <x:c r="I45" s="18">
-        <x:v>45602</x:v>
+        <x:v>45973</x:v>
       </x:c>
       <x:c r="J45" s="17" t="n">
-        <x:v>1216174</x:v>
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K45" s="19" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L45" s="20">
-        <x:v>46093.1514351852</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M45" s="16" t="s">
         <x:v>26</x:v>
@@ -4520,12 +4532,14 @@
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B46" s="16" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="D46" s="17" t="s"/>
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E46" s="16" t="s">
         <x:v>671</x:v>
       </x:c>
@@ -4536,19 +4550,19 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="H46" s="18">
-        <x:v>46090.2854050926</x:v>
+        <x:v>46079.0151851852</x:v>
       </x:c>
       <x:c r="I46" s="18">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J46" s="17" t="s">
-        <x:v>673</x:v>
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J46" s="17" t="n">
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K46" s="19" t="n">
-        <x:v>426</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L46" s="20">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M46" s="16" t="s">
         <x:v>26</x:v>
@@ -4572,19 +4586,19 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="H47" s="18">
-        <x:v>46090.2540972222</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I47" s="18">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J47" s="17" t="n">
-        <x:v>1216185</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J47" s="17" t="s">
+        <x:v>677</x:v>
       </x:c>
       <x:c r="K47" s="19" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L47" s="20">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M47" s="16" t="s">
         <x:v>26</x:v>
@@ -4599,28 +4613,28 @@
       </x:c>
       <x:c r="D48" s="17" t="s"/>
       <x:c r="E48" s="16" t="s">
-        <x:v>675</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="F48" s="16" t="s">
-        <x:v>679</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="G48" s="16" t="s">
-        <x:v>680</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="H48" s="18">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2540972222</x:v>
       </x:c>
       <x:c r="I48" s="18">
-        <x:v>46090.2349305556</x:v>
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J48" s="17" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K48" s="19" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L48" s="20">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M48" s="16" t="s">
         <x:v>26</x:v>
@@ -4628,16 +4642,14 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="16" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C49" s="16" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D49" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="D49" s="17" t="s"/>
       <x:c r="E49" s="16" t="s">
-        <x:v>682</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="F49" s="16" t="s">
         <x:v>683</x:v>
@@ -4646,19 +4658,19 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="H49" s="18">
-        <x:v>46073.0262847222</x:v>
+        <x:v>46090.2349189815</x:v>
       </x:c>
       <x:c r="I49" s="18">
-        <x:v>46042</x:v>
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J49" s="17" t="n">
-        <x:v>1216157</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K49" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L49" s="20">
-        <x:v>46090.267025463</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M49" s="16" t="s">
         <x:v>26</x:v>
@@ -4684,19 +4696,19 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="H50" s="18">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46073.0262847222</x:v>
       </x:c>
       <x:c r="I50" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J50" s="17" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216157</x:v>
       </x:c>
       <x:c r="K50" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L50" s="20">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.267025463</x:v>
       </x:c>
       <x:c r="M50" s="16" t="s">
         <x:v>26</x:v>
@@ -4722,19 +4734,19 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="H51" s="18">
-        <x:v>46073.0478472222</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I51" s="18">
         <x:v>46042</x:v>
       </x:c>
       <x:c r="J51" s="17" t="n">
-        <x:v>1216153</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K51" s="19" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L51" s="20">
-        <x:v>46090.2431828704</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M51" s="16" t="s">
         <x:v>26</x:v>
@@ -4751,28 +4763,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E52" s="16" t="s">
-        <x:v>641</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="F52" s="16" t="s">
-        <x:v>694</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="G52" s="16" t="s">
-        <x:v>695</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="H52" s="18">
-        <x:v>46073.1095023148</x:v>
+        <x:v>46073.0478472222</x:v>
       </x:c>
       <x:c r="I52" s="18">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J52" s="17" t="n">
-        <x:v>1216164</x:v>
+        <x:v>1216153</x:v>
       </x:c>
       <x:c r="K52" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L52" s="20">
-        <x:v>46091.121087963</x:v>
+        <x:v>46090.2431828704</x:v>
       </x:c>
       <x:c r="M52" s="16" t="s">
         <x:v>26</x:v>
@@ -4783,34 +4795,34 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="16" t="s">
-        <x:v>696</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="D53" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="16" t="s">
-        <x:v>641</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F53" s="16" t="s">
-        <x:v>697</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="G53" s="16" t="s">
-        <x:v>698</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="H53" s="18">
-        <x:v>46073.061099537</x:v>
+        <x:v>46073.1095023148</x:v>
       </x:c>
       <x:c r="I53" s="18">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J53" s="17" t="n">
-        <x:v>1216151</x:v>
+        <x:v>1216164</x:v>
       </x:c>
       <x:c r="K53" s="19" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L53" s="20">
-        <x:v>46090.2266435185</x:v>
+        <x:v>46091.121087963</x:v>
       </x:c>
       <x:c r="M53" s="16" t="s">
         <x:v>26</x:v>
@@ -4821,13 +4833,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C54" s="16" t="s">
-        <x:v>699</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="D54" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E54" s="16" t="s">
-        <x:v>700</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F54" s="16" t="s">
         <x:v>701</x:v>
@@ -4836,19 +4848,19 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="H54" s="18">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46073.061099537</x:v>
       </x:c>
       <x:c r="I54" s="18">
-        <x:v>45748</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J54" s="17" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216151</x:v>
       </x:c>
       <x:c r="K54" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L54" s="20">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2266435185</x:v>
       </x:c>
       <x:c r="M54" s="16" t="s">
         <x:v>26</x:v>
@@ -4865,28 +4877,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="16" t="s">
-        <x:v>641</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="F55" s="16" t="s">
-        <x:v>704</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="G55" s="16" t="s">
-        <x:v>705</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="H55" s="18">
-        <x:v>46073.0763541667</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I55" s="18">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J55" s="17" t="n">
-        <x:v>1216149</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K55" s="19" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L55" s="20">
-        <x:v>46090.2162847222</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M55" s="16" t="s">
         <x:v>26</x:v>
@@ -4897,13 +4909,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C56" s="16" t="s">
-        <x:v>706</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D56" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="16" t="s">
-        <x:v>707</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F56" s="16" t="s">
         <x:v>708</x:v>
@@ -4912,19 +4924,19 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="H56" s="18">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46073.0763541667</x:v>
       </x:c>
       <x:c r="I56" s="18">
-        <x:v>46115</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J56" s="17" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216149</x:v>
       </x:c>
       <x:c r="K56" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L56" s="20">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2162847222</x:v>
       </x:c>
       <x:c r="M56" s="16" t="s">
         <x:v>26</x:v>
@@ -4950,19 +4962,19 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="H57" s="18">
-        <x:v>46071.2853587963</x:v>
+        <x:v>46077.1834259259</x:v>
       </x:c>
       <x:c r="I57" s="18">
-        <x:v>45748</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J57" s="17" t="n">
-        <x:v>1216191</x:v>
+        <x:v>1216166</x:v>
       </x:c>
       <x:c r="K57" s="19" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="20">
-        <x:v>46094.1777199074</x:v>
+        <x:v>46091.2388773148</x:v>
       </x:c>
       <x:c r="M57" s="16" t="s">
         <x:v>26</x:v>
@@ -4988,71 +5000,98 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="H58" s="18">
-        <x:v>46090.3681365741</x:v>
+        <x:v>46071.2853587963</x:v>
       </x:c>
       <x:c r="I58" s="18">
-        <x:v>46101</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J58" s="17" t="n">
-        <x:v>1216192</x:v>
+        <x:v>1216191</x:v>
       </x:c>
       <x:c r="K58" s="19" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L58" s="20">
-        <x:v>46094.182662037</x:v>
+        <x:v>46094.1777199074</x:v>
       </x:c>
       <x:c r="M58" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B59" s="16" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="D59" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="H59" s="18">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I59" s="18">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J59" s="17" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K59" s="19" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L59" s="20">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M59" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B61" s="21" t="s">
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B62" s="21" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C61" s="22" t="s"/>
-      <x:c r="D61" s="22" t="s"/>
-      <x:c r="E61" s="23" t="s"/>
-      <x:c r="F61" s="23" t="s"/>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B62" s="24" t="s">
+      <x:c r="C62" s="22" t="s"/>
+      <x:c r="D62" s="22" t="s"/>
+      <x:c r="E62" s="23" t="s"/>
+      <x:c r="F62" s="23" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B63" s="24" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C62" s="25" t="s"/>
-      <x:c r="D62" s="25" t="s"/>
-      <x:c r="E62" s="25" t="s"/>
-      <x:c r="F62" s="26" t="s">
+      <x:c r="C63" s="25" t="s"/>
+      <x:c r="D63" s="25" t="s"/>
+      <x:c r="E63" s="25" t="s"/>
+      <x:c r="F63" s="26" t="s">
         <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B63" s="27" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C63" s="28" t="s"/>
-      <x:c r="D63" s="28" t="s"/>
-      <x:c r="E63" s="28" t="s"/>
-      <x:c r="F63" s="29" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="18" customHeight="1">
       <x:c r="B64" s="27" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C64" s="28" t="s"/>
       <x:c r="D64" s="28" t="s"/>
       <x:c r="E64" s="28" t="s"/>
       <x:c r="F64" s="29" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:28" ht="18" customHeight="1">
       <x:c r="B65" s="27" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C65" s="28" t="s"/>
       <x:c r="D65" s="28" t="s"/>
@@ -5063,7 +5102,7 @@
     </x:row>
     <x:row r="66" spans="1:28" ht="18" customHeight="1">
       <x:c r="B66" s="27" t="s">
-        <x:v>113</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C66" s="28" t="s"/>
       <x:c r="D66" s="28" t="s"/>
@@ -5074,82 +5113,92 @@
     </x:row>
     <x:row r="67" spans="1:28" ht="18" customHeight="1">
       <x:c r="B67" s="27" t="s">
-        <x:v>305</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C67" s="28" t="s"/>
       <x:c r="D67" s="28" t="s"/>
       <x:c r="E67" s="28" t="s"/>
       <x:c r="F67" s="29" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="18" customHeight="1">
       <x:c r="B68" s="27" t="s">
-        <x:v>14</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C68" s="28" t="s"/>
       <x:c r="D68" s="28" t="s"/>
       <x:c r="E68" s="28" t="s"/>
       <x:c r="F68" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="18" customHeight="1">
       <x:c r="B69" s="27" t="s">
-        <x:v>608</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C69" s="28" t="s"/>
       <x:c r="D69" s="28" t="s"/>
       <x:c r="E69" s="28" t="s"/>
       <x:c r="F69" s="29" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="18" customHeight="1">
       <x:c r="B70" s="27" t="s">
-        <x:v>21</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C70" s="28" t="s"/>
       <x:c r="D70" s="28" t="s"/>
       <x:c r="E70" s="28" t="s"/>
       <x:c r="F70" s="29" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="18" customHeight="1">
       <x:c r="B71" s="27" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C71" s="28" t="s"/>
       <x:c r="D71" s="28" t="s"/>
       <x:c r="E71" s="28" t="s"/>
       <x:c r="F71" s="29" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="18" customHeight="1">
       <x:c r="B72" s="27" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C72" s="28" t="s"/>
       <x:c r="D72" s="28" t="s"/>
       <x:c r="E72" s="28" t="s"/>
       <x:c r="F72" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B73" s="27" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C73" s="28" t="s"/>
+      <x:c r="D73" s="28" t="s"/>
+      <x:c r="E73" s="28" t="s"/>
+      <x:c r="F73" s="29" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B73" s="30" t="s">
+    <x:row r="74" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B74" s="30" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C73" s="31" t="s"/>
-      <x:c r="D73" s="31" t="s"/>
-      <x:c r="E73" s="31" t="s"/>
-      <x:c r="F73" s="32" t="n">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C74" s="31" t="s"/>
+      <x:c r="D74" s="31" t="s"/>
+      <x:c r="E74" s="31" t="s"/>
+      <x:c r="F74" s="32" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6074,8 +6123,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B61:F61"/>
-    <x:mergeCell ref="B62:E62"/>
+    <x:mergeCell ref="B62:F62"/>
     <x:mergeCell ref="B63:E63"/>
     <x:mergeCell ref="B64:E64"/>
     <x:mergeCell ref="B65:E65"/>
@@ -6087,6 +6135,7 @@
     <x:mergeCell ref="B71:E71"/>
     <x:mergeCell ref="B72:E72"/>
     <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B74:E74"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="902">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="907">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2124,6 +2124,21 @@
     <x:t>1217027</x:t>
   </x:si>
   <x:si>
+    <x:t>PMC EXPRESS HUB INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit no. 227, Robinson Pagadian Mall, F.S. Pajares Ave., Cor. P.L. Urro St., Cor Vincenzo, Sagun St.,, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-II0618A-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1391-148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216201</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARTURO D ANTONIO</x:t>
   </x:si>
   <x:si>
@@ -2538,6 +2553,18 @@
     <x:t>1216143</x:t>
   </x:si>
   <x:si>
+    <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1281-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1372-847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216174</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-1283-23</x:t>
   </x:si>
   <x:si>
@@ -2545,18 +2572,6 @@
   </x:si>
   <x:si>
     <x:t>1216173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-1281-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1372-847</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216174</x:t>
   </x:si>
   <x:si>
     <x:t>AILYN G. PANIS</x:t>
@@ -3905,7 +3920,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="13" t="s">
-        <x:v>133</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C16" s="13" t="s">
         <x:v>697</x:v>
@@ -3923,19 +3938,19 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="H16" s="15">
-        <x:v>46072.3153026736</x:v>
+        <x:v>46091.1989145023</x:v>
       </x:c>
       <x:c r="I16" s="15">
-        <x:v>46114</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J16" s="14" t="s">
         <x:v>701</x:v>
       </x:c>
       <x:c r="K16" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L16" s="17">
-        <x:v>46090.3114235417</x:v>
+        <x:v>46106.1492534144</x:v>
       </x:c>
       <x:c r="M16" s="13" t="s">
         <x:v>28</x:v>
@@ -3943,13 +3958,13 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="13" t="s">
-        <x:v>371</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C17" s="13" t="s">
         <x:v>702</x:v>
       </x:c>
       <x:c r="D17" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="13" t="s">
         <x:v>703</x:v>
@@ -3961,19 +3976,19 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="H17" s="15">
-        <x:v>46076.2810036343</x:v>
+        <x:v>46072.3153026736</x:v>
       </x:c>
       <x:c r="I17" s="15">
-        <x:v>46076.2810195833</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="J17" s="14" t="s">
         <x:v>706</x:v>
       </x:c>
       <x:c r="K17" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L17" s="17">
-        <x:v>46097.2411206366</x:v>
+        <x:v>46090.3114235417</x:v>
       </x:c>
       <x:c r="M17" s="13" t="s">
         <x:v>28</x:v>
@@ -3999,10 +4014,10 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="H18" s="15">
-        <x:v>46076.2450058565</x:v>
+        <x:v>46076.2810036343</x:v>
       </x:c>
       <x:c r="I18" s="15">
-        <x:v>46076.2450229514</x:v>
+        <x:v>46076.2810195833</x:v>
       </x:c>
       <x:c r="J18" s="14" t="s">
         <x:v>711</x:v>
@@ -4011,7 +4026,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="17">
-        <x:v>46094.1710418981</x:v>
+        <x:v>46097.2411206366</x:v>
       </x:c>
       <x:c r="M18" s="13" t="s">
         <x:v>28</x:v>
@@ -4037,10 +4052,10 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="H19" s="15">
-        <x:v>46076.2578122338</x:v>
+        <x:v>46076.2450058565</x:v>
       </x:c>
       <x:c r="I19" s="15">
-        <x:v>46076.2578276505</x:v>
+        <x:v>46076.2450229514</x:v>
       </x:c>
       <x:c r="J19" s="14" t="s">
         <x:v>716</x:v>
@@ -4049,7 +4064,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="17">
-        <x:v>46097.2583940162</x:v>
+        <x:v>46094.1710418981</x:v>
       </x:c>
       <x:c r="M19" s="13" t="s">
         <x:v>28</x:v>
@@ -4075,19 +4090,19 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="H20" s="15">
-        <x:v>46076.263358912</x:v>
+        <x:v>46076.2578122338</x:v>
       </x:c>
       <x:c r="I20" s="15">
-        <x:v>46076.2633790625</x:v>
+        <x:v>46076.2578276505</x:v>
       </x:c>
       <x:c r="J20" s="14" t="s">
         <x:v>721</x:v>
       </x:c>
       <x:c r="K20" s="16" t="n">
-        <x:v>4530</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L20" s="17">
-        <x:v>46094.1562770949</x:v>
+        <x:v>46097.2583940162</x:v>
       </x:c>
       <x:c r="M20" s="13" t="s">
         <x:v>28</x:v>
@@ -4113,19 +4128,19 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="H21" s="15">
-        <x:v>46076.3755334722</x:v>
+        <x:v>46076.263358912</x:v>
       </x:c>
       <x:c r="I21" s="15">
-        <x:v>46076.3755506134</x:v>
+        <x:v>46076.2633790625</x:v>
       </x:c>
       <x:c r="J21" s="14" t="s">
         <x:v>726</x:v>
       </x:c>
       <x:c r="K21" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L21" s="17">
-        <x:v>46094.1653946759</x:v>
+        <x:v>46094.1562770949</x:v>
       </x:c>
       <x:c r="M21" s="13" t="s">
         <x:v>28</x:v>
@@ -4133,13 +4148,13 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
         <x:v>727</x:v>
       </x:c>
       <x:c r="D22" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
         <x:v>728</x:v>
@@ -4151,19 +4166,19 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="H22" s="15">
-        <x:v>46083.2966067014</x:v>
+        <x:v>46076.3755334722</x:v>
       </x:c>
       <x:c r="I22" s="15">
-        <x:v>46387</x:v>
+        <x:v>46076.3755506134</x:v>
       </x:c>
       <x:c r="J22" s="14" t="s">
         <x:v>731</x:v>
       </x:c>
       <x:c r="K22" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L22" s="17">
-        <x:v>46098.2996351505</x:v>
+        <x:v>46094.1653946759</x:v>
       </x:c>
       <x:c r="M22" s="13" t="s">
         <x:v>28</x:v>
@@ -4189,10 +4204,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="H23" s="15">
-        <x:v>46046.1343687731</x:v>
+        <x:v>46083.2966067014</x:v>
       </x:c>
       <x:c r="I23" s="15">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J23" s="14" t="s">
         <x:v>736</x:v>
@@ -4201,7 +4216,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="17">
-        <x:v>46093.2878737037</x:v>
+        <x:v>46098.2996351505</x:v>
       </x:c>
       <x:c r="M23" s="13" t="s">
         <x:v>28</x:v>
@@ -4227,19 +4242,19 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="H24" s="15">
-        <x:v>46046.1309132176</x:v>
+        <x:v>46046.1343687731</x:v>
       </x:c>
       <x:c r="I24" s="15">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J24" s="14" t="s">
         <x:v>741</x:v>
       </x:c>
       <x:c r="K24" s="16" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="17">
-        <x:v>46093.2732890162</x:v>
+        <x:v>46093.2878737037</x:v>
       </x:c>
       <x:c r="M24" s="13" t="s">
         <x:v>28</x:v>
@@ -4250,34 +4265,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
-        <x:v>737</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="D25" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="13" t="s">
-        <x:v>742</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="F25" s="13" t="s">
-        <x:v>743</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="G25" s="13" t="s">
-        <x:v>744</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="H25" s="15">
-        <x:v>46046.1237709144</x:v>
+        <x:v>46046.1309132176</x:v>
       </x:c>
       <x:c r="I25" s="15">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J25" s="14" t="s">
-        <x:v>745</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="K25" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L25" s="17">
-        <x:v>46093.2636364931</x:v>
+        <x:v>46093.2732890162</x:v>
       </x:c>
       <x:c r="M25" s="13" t="s">
         <x:v>28</x:v>
@@ -4288,7 +4303,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="13" t="s">
-        <x:v>746</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
         <x:v>16</x:v>
@@ -4303,10 +4318,10 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="H26" s="15">
-        <x:v>46046.1140924306</x:v>
+        <x:v>46046.1237709144</x:v>
       </x:c>
       <x:c r="I26" s="15">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J26" s="14" t="s">
         <x:v>750</x:v>
@@ -4315,7 +4330,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="17">
-        <x:v>46093.2825289005</x:v>
+        <x:v>46093.2636364931</x:v>
       </x:c>
       <x:c r="M26" s="13" t="s">
         <x:v>28</x:v>
@@ -4341,10 +4356,10 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="H27" s="15">
-        <x:v>46048.0974875347</x:v>
+        <x:v>46046.1140924306</x:v>
       </x:c>
       <x:c r="I27" s="15">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J27" s="14" t="s">
         <x:v>755</x:v>
@@ -4353,7 +4368,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="17">
-        <x:v>46093.2926065278</x:v>
+        <x:v>46093.2825289005</x:v>
       </x:c>
       <x:c r="M27" s="13" t="s">
         <x:v>28</x:v>
@@ -4379,10 +4394,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="H28" s="15">
-        <x:v>46076.3189094676</x:v>
+        <x:v>46048.0974875347</x:v>
       </x:c>
       <x:c r="I28" s="15">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J28" s="14" t="s">
         <x:v>760</x:v>
@@ -4391,7 +4406,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L28" s="17">
-        <x:v>46092.1400343403</x:v>
+        <x:v>46093.2926065278</x:v>
       </x:c>
       <x:c r="M28" s="13" t="s">
         <x:v>28</x:v>
@@ -4399,13 +4414,13 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="C29" s="13" t="s">
-        <x:v>702</x:v>
-      </x:c>
       <x:c r="D29" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="13" t="s">
         <x:v>762</x:v>
@@ -4417,19 +4432,19 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="H29" s="15">
-        <x:v>46079.2852568981</x:v>
+        <x:v>46076.3189094676</x:v>
       </x:c>
       <x:c r="I29" s="15">
-        <x:v>46079.2852718981</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J29" s="14" t="s">
         <x:v>765</x:v>
       </x:c>
       <x:c r="K29" s="16" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="17">
-        <x:v>46097.2459243171</x:v>
+        <x:v>46092.1400343403</x:v>
       </x:c>
       <x:c r="M29" s="13" t="s">
         <x:v>28</x:v>
@@ -4437,37 +4452,37 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B30" s="13" t="s">
-        <x:v>761</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="C30" s="13" t="s">
-        <x:v>712</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D30" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E30" s="13" t="s">
-        <x:v>766</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="F30" s="13" t="s">
-        <x:v>767</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="G30" s="13" t="s">
-        <x:v>768</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="H30" s="15">
-        <x:v>46079.2747337153</x:v>
+        <x:v>46079.2852568981</x:v>
       </x:c>
       <x:c r="I30" s="15">
-        <x:v>46079.2747495718</x:v>
+        <x:v>46079.2852718981</x:v>
       </x:c>
       <x:c r="J30" s="14" t="s">
-        <x:v>769</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="K30" s="16" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L30" s="17">
-        <x:v>46097.2536368518</x:v>
+        <x:v>46097.2459243171</x:v>
       </x:c>
       <x:c r="M30" s="13" t="s">
         <x:v>28</x:v>
@@ -4475,13 +4490,13 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>770</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="D31" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
         <x:v>771</x:v>
@@ -4493,19 +4508,19 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="H31" s="15">
-        <x:v>46076.1792420602</x:v>
+        <x:v>46079.2747337153</x:v>
       </x:c>
       <x:c r="I31" s="15">
-        <x:v>46058</x:v>
+        <x:v>46079.2747495718</x:v>
       </x:c>
       <x:c r="J31" s="14" t="s">
         <x:v>774</x:v>
       </x:c>
       <x:c r="K31" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L31" s="17">
-        <x:v>46090.204281088</x:v>
+        <x:v>46097.2536368518</x:v>
       </x:c>
       <x:c r="M31" s="13" t="s">
         <x:v>28</x:v>
@@ -4516,34 +4531,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="13" t="s">
-        <x:v>770</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="D32" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="13" t="s">
-        <x:v>775</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="F32" s="13" t="s">
-        <x:v>776</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="G32" s="13" t="s">
-        <x:v>777</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="H32" s="15">
-        <x:v>46072.0333546991</x:v>
+        <x:v>46076.1792420602</x:v>
       </x:c>
       <x:c r="I32" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J32" s="14" t="s">
-        <x:v>778</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="K32" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="17">
-        <x:v>46090.2584930556</x:v>
+        <x:v>46090.204281088</x:v>
       </x:c>
       <x:c r="M32" s="13" t="s">
         <x:v>28</x:v>
@@ -4554,7 +4569,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="13" t="s">
-        <x:v>779</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="D33" s="14" t="s">
         <x:v>16</x:v>
@@ -4569,7 +4584,7 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="H33" s="15">
-        <x:v>46071.1677711806</x:v>
+        <x:v>46072.0333546991</x:v>
       </x:c>
       <x:c r="I33" s="15">
         <x:v>46058</x:v>
@@ -4581,7 +4596,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L33" s="17">
-        <x:v>46091.1948946528</x:v>
+        <x:v>46090.2584930556</x:v>
       </x:c>
       <x:c r="M33" s="13" t="s">
         <x:v>28</x:v>
@@ -4607,19 +4622,19 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="H34" s="15">
-        <x:v>46070.1768476389</x:v>
+        <x:v>46071.1677711806</x:v>
       </x:c>
       <x:c r="I34" s="15">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J34" s="14" t="s">
         <x:v>788</x:v>
       </x:c>
       <x:c r="K34" s="16" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L34" s="17">
-        <x:v>46084.1495253588</x:v>
+        <x:v>46091.1948946528</x:v>
       </x:c>
       <x:c r="M34" s="13" t="s">
         <x:v>28</x:v>
@@ -4645,10 +4660,10 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="H35" s="15">
-        <x:v>46076.1139638194</x:v>
+        <x:v>46070.1768476389</x:v>
       </x:c>
       <x:c r="I35" s="15">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J35" s="14" t="s">
         <x:v>793</x:v>
@@ -4657,7 +4672,7 @@
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L35" s="17">
-        <x:v>46090.1919488889</x:v>
+        <x:v>46084.1495253588</x:v>
       </x:c>
       <x:c r="M35" s="13" t="s">
         <x:v>28</x:v>
@@ -4668,34 +4683,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C36" s="13" t="s">
-        <x:v>624</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="D36" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="13" t="s">
-        <x:v>794</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="F36" s="13" t="s">
-        <x:v>795</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="G36" s="13" t="s">
-        <x:v>796</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="H36" s="15">
-        <x:v>46071.3305731597</x:v>
+        <x:v>46076.1139638194</x:v>
       </x:c>
       <x:c r="I36" s="15">
-        <x:v>46112</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J36" s="14" t="s">
-        <x:v>797</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="K36" s="16" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L36" s="17">
-        <x:v>46094.1906452199</x:v>
+        <x:v>46090.1919488889</x:v>
       </x:c>
       <x:c r="M36" s="13" t="s">
         <x:v>28</x:v>
@@ -4706,7 +4721,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="13" t="s">
-        <x:v>798</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D37" s="14" t="s">
         <x:v>16</x:v>
@@ -4721,19 +4736,19 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="H37" s="15">
-        <x:v>46077.2598841551</x:v>
+        <x:v>46071.3305731597</x:v>
       </x:c>
       <x:c r="I37" s="15">
-        <x:v>46058</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J37" s="14" t="s">
         <x:v>802</x:v>
       </x:c>
       <x:c r="K37" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L37" s="17">
-        <x:v>46090.2758708681</x:v>
+        <x:v>46094.1906452199</x:v>
       </x:c>
       <x:c r="M37" s="13" t="s">
         <x:v>28</x:v>
@@ -4744,34 +4759,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="13" t="s">
-        <x:v>798</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D38" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="13" t="s">
-        <x:v>803</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F38" s="13" t="s">
-        <x:v>804</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="G38" s="13" t="s">
-        <x:v>805</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="H38" s="15">
-        <x:v>46072.1089512963</x:v>
+        <x:v>46077.2598841551</x:v>
       </x:c>
       <x:c r="I38" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J38" s="14" t="s">
-        <x:v>806</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="K38" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L38" s="17">
-        <x:v>46090.2365117824</x:v>
+        <x:v>46090.2758708681</x:v>
       </x:c>
       <x:c r="M38" s="13" t="s">
         <x:v>28</x:v>
@@ -4782,34 +4797,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="13" t="s">
-        <x:v>798</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D39" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="13" t="s">
-        <x:v>807</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="F39" s="13" t="s">
-        <x:v>808</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="G39" s="13" t="s">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="H39" s="15">
-        <x:v>46072.0792950116</x:v>
+        <x:v>46072.1089512963</x:v>
       </x:c>
       <x:c r="I39" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J39" s="14" t="s">
-        <x:v>810</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="K39" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L39" s="17">
-        <x:v>46090.220792662</x:v>
+        <x:v>46090.2365117824</x:v>
       </x:c>
       <x:c r="M39" s="13" t="s">
         <x:v>28</x:v>
@@ -4820,7 +4835,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="13" t="s">
-        <x:v>811</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D40" s="14" t="s">
         <x:v>16</x:v>
@@ -4835,10 +4850,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="H40" s="15">
-        <x:v>46077.4722378472</x:v>
+        <x:v>46072.0792950116</x:v>
       </x:c>
       <x:c r="I40" s="15">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J40" s="14" t="s">
         <x:v>815</x:v>
@@ -4847,7 +4862,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L40" s="17">
-        <x:v>46090.2963156019</x:v>
+        <x:v>46090.220792662</x:v>
       </x:c>
       <x:c r="M40" s="13" t="s">
         <x:v>28</x:v>
@@ -4858,34 +4873,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="13" t="s">
-        <x:v>811</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D41" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="F41" s="13" t="s">
-        <x:v>817</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="G41" s="13" t="s">
-        <x:v>818</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="H41" s="15">
-        <x:v>46077.5191885417</x:v>
+        <x:v>46077.4722378472</x:v>
       </x:c>
       <x:c r="I41" s="15">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J41" s="14" t="s">
-        <x:v>819</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="K41" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L41" s="17">
-        <x:v>46090.3155018056</x:v>
+        <x:v>46090.2963156019</x:v>
       </x:c>
       <x:c r="M41" s="13" t="s">
         <x:v>28</x:v>
@@ -4896,34 +4911,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
-        <x:v>811</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D42" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="13" t="s">
-        <x:v>820</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="F42" s="13" t="s">
-        <x:v>821</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="G42" s="13" t="s">
-        <x:v>822</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="H42" s="15">
-        <x:v>46072.0497342708</x:v>
+        <x:v>46077.5191885417</x:v>
       </x:c>
       <x:c r="I42" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J42" s="14" t="s">
-        <x:v>823</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="K42" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L42" s="17">
-        <x:v>46090.2102464352</x:v>
+        <x:v>46090.3155018056</x:v>
       </x:c>
       <x:c r="M42" s="13" t="s">
         <x:v>28</x:v>
@@ -4934,34 +4949,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C43" s="13" t="s">
-        <x:v>811</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D43" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="13" t="s">
-        <x:v>807</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="F43" s="13" t="s">
-        <x:v>824</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="G43" s="13" t="s">
-        <x:v>825</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="H43" s="15">
-        <x:v>46077.2024189931</x:v>
+        <x:v>46072.0497342708</x:v>
       </x:c>
       <x:c r="I43" s="15">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J43" s="14" t="s">
-        <x:v>826</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="K43" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L43" s="17">
-        <x:v>46090.2496018056</x:v>
+        <x:v>46090.2102464352</x:v>
       </x:c>
       <x:c r="M43" s="13" t="s">
         <x:v>28</x:v>
@@ -4972,13 +4987,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C44" s="13" t="s">
-        <x:v>827</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D44" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="13" t="s">
-        <x:v>828</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="F44" s="13" t="s">
         <x:v>829</x:v>
@@ -4987,10 +5002,10 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="H44" s="15">
-        <x:v>46071.2072683796</x:v>
+        <x:v>46077.2024189931</x:v>
       </x:c>
       <x:c r="I44" s="15">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J44" s="14" t="s">
         <x:v>831</x:v>
@@ -4999,7 +5014,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L44" s="17">
-        <x:v>46090.0616673032</x:v>
+        <x:v>46090.2496018056</x:v>
       </x:c>
       <x:c r="M44" s="13" t="s">
         <x:v>28</x:v>
@@ -5010,34 +5025,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C45" s="13" t="s">
-        <x:v>827</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="D45" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="13" t="s">
-        <x:v>807</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="F45" s="13" t="s">
-        <x:v>832</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="G45" s="13" t="s">
-        <x:v>833</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="H45" s="15">
-        <x:v>46071.2285509838</x:v>
+        <x:v>46071.2072683796</x:v>
       </x:c>
       <x:c r="I45" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J45" s="14" t="s">
-        <x:v>834</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="K45" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L45" s="17">
-        <x:v>46090.0772934491</x:v>
+        <x:v>46090.0616673032</x:v>
       </x:c>
       <x:c r="M45" s="13" t="s">
         <x:v>28</x:v>
@@ -5048,34 +5063,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C46" s="13" t="s">
-        <x:v>320</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="D46" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="13" t="s">
-        <x:v>321</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="F46" s="13" t="s">
-        <x:v>835</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="G46" s="13" t="s">
-        <x:v>836</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="H46" s="15">
-        <x:v>45988.189350544</x:v>
+        <x:v>46071.2285509838</x:v>
       </x:c>
       <x:c r="I46" s="15">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J46" s="14" t="s">
-        <x:v>837</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="K46" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L46" s="17">
-        <x:v>46093.1383928935</x:v>
+        <x:v>46090.0772934491</x:v>
       </x:c>
       <x:c r="M46" s="13" t="s">
         <x:v>28</x:v>
@@ -5092,13 +5107,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E47" s="13" t="s">
-        <x:v>838</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="F47" s="13" t="s">
-        <x:v>839</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="G47" s="13" t="s">
-        <x:v>840</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="H47" s="15">
         <x:v>46079.0151889352</x:v>
@@ -5107,7 +5122,7 @@
         <x:v>45602</x:v>
       </x:c>
       <x:c r="J47" s="14" t="s">
-        <x:v>841</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="K47" s="16" t="n">
         <x:v>3990</x:v>
@@ -5121,14 +5136,16 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C48" s="13" t="s">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="D48" s="14" t="s"/>
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E48" s="13" t="s">
-        <x:v>843</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F48" s="13" t="s">
         <x:v>844</x:v>
@@ -5137,19 +5154,19 @@
         <x:v>845</x:v>
       </x:c>
       <x:c r="H48" s="15">
-        <x:v>46090.2854096643</x:v>
+        <x:v>45988.189350544</x:v>
       </x:c>
       <x:c r="I48" s="15">
-        <x:v>46090.2854287153</x:v>
+        <x:v>45973</x:v>
       </x:c>
       <x:c r="J48" s="14" t="s">
-        <x:v>845</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="K48" s="16" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L48" s="17">
-        <x:v>46094.0865837153</x:v>
+        <x:v>46093.1383928935</x:v>
       </x:c>
       <x:c r="M48" s="13" t="s">
         <x:v>28</x:v>
@@ -5160,23 +5177,23 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C49" s="13" t="s">
-        <x:v>846</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="D49" s="14" t="s"/>
       <x:c r="E49" s="13" t="s">
-        <x:v>847</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="F49" s="13" t="s">
-        <x:v>848</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="G49" s="13" t="s">
-        <x:v>849</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="H49" s="15">
-        <x:v>46090.2541037731</x:v>
+        <x:v>46090.2854096643</x:v>
       </x:c>
       <x:c r="I49" s="15">
-        <x:v>46090.2541222106</x:v>
+        <x:v>46090.2854287153</x:v>
       </x:c>
       <x:c r="J49" s="14" t="s">
         <x:v>850</x:v>
@@ -5185,7 +5202,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="L49" s="17">
-        <x:v>46094.0819034491</x:v>
+        <x:v>46094.0865837153</x:v>
       </x:c>
       <x:c r="M49" s="13" t="s">
         <x:v>28</x:v>
@@ -5200,28 +5217,28 @@
       </x:c>
       <x:c r="D50" s="14" t="s"/>
       <x:c r="E50" s="13" t="s">
-        <x:v>847</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="F50" s="13" t="s">
-        <x:v>852</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="G50" s="13" t="s">
-        <x:v>853</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="H50" s="15">
-        <x:v>46090.2349194444</x:v>
+        <x:v>46090.2541037731</x:v>
       </x:c>
       <x:c r="I50" s="15">
-        <x:v>46090.2349374884</x:v>
+        <x:v>46090.2541222106</x:v>
       </x:c>
       <x:c r="J50" s="14" t="s">
-        <x:v>854</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="K50" s="16" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L50" s="17">
-        <x:v>46094.093939213</x:v>
+        <x:v>46094.0819034491</x:v>
       </x:c>
       <x:c r="M50" s="13" t="s">
         <x:v>28</x:v>
@@ -5229,16 +5246,14 @@
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B51" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C51" s="13" t="s">
-        <x:v>855</x:v>
-      </x:c>
-      <x:c r="D51" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="s"/>
       <x:c r="E51" s="13" t="s">
-        <x:v>856</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="F51" s="13" t="s">
         <x:v>857</x:v>
@@ -5247,19 +5262,19 @@
         <x:v>858</x:v>
       </x:c>
       <x:c r="H51" s="15">
-        <x:v>46073.0262962616</x:v>
+        <x:v>46090.2349194444</x:v>
       </x:c>
       <x:c r="I51" s="15">
-        <x:v>46042</x:v>
+        <x:v>46090.2349374884</x:v>
       </x:c>
       <x:c r="J51" s="14" t="s">
         <x:v>859</x:v>
       </x:c>
       <x:c r="K51" s="16" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L51" s="17">
-        <x:v>46090.2670310069</x:v>
+        <x:v>46094.093939213</x:v>
       </x:c>
       <x:c r="M51" s="13" t="s">
         <x:v>28</x:v>
@@ -5285,7 +5300,7 @@
         <x:v>863</x:v>
       </x:c>
       <x:c r="H52" s="15">
-        <x:v>46077.2103691435</x:v>
+        <x:v>46073.0262962616</x:v>
       </x:c>
       <x:c r="I52" s="15">
         <x:v>46042</x:v>
@@ -5297,7 +5312,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L52" s="17">
-        <x:v>46090.253629537</x:v>
+        <x:v>46090.2670310069</x:v>
       </x:c>
       <x:c r="M52" s="13" t="s">
         <x:v>28</x:v>
@@ -5323,7 +5338,7 @@
         <x:v>868</x:v>
       </x:c>
       <x:c r="H53" s="15">
-        <x:v>46073.0478536458</x:v>
+        <x:v>46077.2103691435</x:v>
       </x:c>
       <x:c r="I53" s="15">
         <x:v>46042</x:v>
@@ -5335,7 +5350,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L53" s="17">
-        <x:v>46090.2431909954</x:v>
+        <x:v>46090.253629537</x:v>
       </x:c>
       <x:c r="M53" s="13" t="s">
         <x:v>28</x:v>
@@ -5352,28 +5367,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E54" s="13" t="s">
-        <x:v>799</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="F54" s="13" t="s">
-        <x:v>871</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="G54" s="13" t="s">
-        <x:v>872</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="H54" s="15">
-        <x:v>46073.10951125</x:v>
+        <x:v>46073.0478536458</x:v>
       </x:c>
       <x:c r="I54" s="15">
-        <x:v>45824</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J54" s="14" t="s">
-        <x:v>873</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="K54" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L54" s="17">
-        <x:v>46091.1210900116</x:v>
+        <x:v>46090.2431909954</x:v>
       </x:c>
       <x:c r="M54" s="13" t="s">
         <x:v>28</x:v>
@@ -5384,34 +5399,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C55" s="13" t="s">
-        <x:v>874</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="D55" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="13" t="s">
-        <x:v>799</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F55" s="13" t="s">
-        <x:v>875</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="G55" s="13" t="s">
-        <x:v>876</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="H55" s="15">
-        <x:v>46073.0611031366</x:v>
+        <x:v>46073.10951125</x:v>
       </x:c>
       <x:c r="I55" s="15">
-        <x:v>46036</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J55" s="14" t="s">
-        <x:v>877</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="K55" s="16" t="n">
-        <x:v>240</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L55" s="17">
-        <x:v>46090.2266513079</x:v>
+        <x:v>46091.1210900116</x:v>
       </x:c>
       <x:c r="M55" s="13" t="s">
         <x:v>28</x:v>
@@ -5422,13 +5437,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="13" t="s">
-        <x:v>878</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="D56" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="13" t="s">
-        <x:v>879</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F56" s="13" t="s">
         <x:v>880</x:v>
@@ -5437,19 +5452,19 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="H56" s="15">
-        <x:v>46077.2683575231</x:v>
+        <x:v>46073.0611031366</x:v>
       </x:c>
       <x:c r="I56" s="15">
-        <x:v>45748</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="J56" s="14" t="s">
         <x:v>882</x:v>
       </x:c>
       <x:c r="K56" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L56" s="17">
-        <x:v>46090.2806125347</x:v>
+        <x:v>46090.2266513079</x:v>
       </x:c>
       <x:c r="M56" s="13" t="s">
         <x:v>28</x:v>
@@ -5466,28 +5481,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="13" t="s">
-        <x:v>799</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="F57" s="13" t="s">
-        <x:v>884</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="G57" s="13" t="s">
-        <x:v>885</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="H57" s="15">
-        <x:v>46073.0763545833</x:v>
+        <x:v>46077.2683575231</x:v>
       </x:c>
       <x:c r="I57" s="15">
-        <x:v>45824</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J57" s="14" t="s">
-        <x:v>886</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="K57" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L57" s="17">
-        <x:v>46090.2162962268</x:v>
+        <x:v>46090.2806125347</x:v>
       </x:c>
       <x:c r="M57" s="13" t="s">
         <x:v>28</x:v>
@@ -5498,13 +5513,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="13" t="s">
-        <x:v>887</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="D58" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="13" t="s">
-        <x:v>888</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F58" s="13" t="s">
         <x:v>889</x:v>
@@ -5513,19 +5528,19 @@
         <x:v>890</x:v>
       </x:c>
       <x:c r="H58" s="15">
-        <x:v>46077.1834319213</x:v>
+        <x:v>46073.0763545833</x:v>
       </x:c>
       <x:c r="I58" s="15">
-        <x:v>46115</x:v>
+        <x:v>45824</x:v>
       </x:c>
       <x:c r="J58" s="14" t="s">
         <x:v>891</x:v>
       </x:c>
       <x:c r="K58" s="16" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L58" s="17">
-        <x:v>46091.2388780324</x:v>
+        <x:v>46090.2162962268</x:v>
       </x:c>
       <x:c r="M58" s="13" t="s">
         <x:v>28</x:v>
@@ -5551,19 +5566,19 @@
         <x:v>895</x:v>
       </x:c>
       <x:c r="H59" s="15">
-        <x:v>46071.2853697569</x:v>
+        <x:v>46077.1834319213</x:v>
       </x:c>
       <x:c r="I59" s="15">
-        <x:v>45748</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J59" s="14" t="s">
         <x:v>896</x:v>
       </x:c>
       <x:c r="K59" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="17">
-        <x:v>46094.1777229282</x:v>
+        <x:v>46091.2388780324</x:v>
       </x:c>
       <x:c r="M59" s="13" t="s">
         <x:v>28</x:v>
@@ -5589,71 +5604,98 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="H60" s="15">
-        <x:v>46090.3681394907</x:v>
+        <x:v>46071.2853697569</x:v>
       </x:c>
       <x:c r="I60" s="15">
-        <x:v>46101</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J60" s="14" t="s">
         <x:v>901</x:v>
       </x:c>
       <x:c r="K60" s="16" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L60" s="17">
-        <x:v>46094.1826630093</x:v>
+        <x:v>46094.1777229282</x:v>
       </x:c>
       <x:c r="M60" s="13" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B61" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C61" s="13" t="s">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E61" s="13" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="F61" s="13" t="s">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="G61" s="13" t="s">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="H61" s="15">
+        <x:v>46090.3681394907</x:v>
+      </x:c>
+      <x:c r="I61" s="15">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J61" s="14" t="s">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="K61" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L61" s="17">
+        <x:v>46094.1826630093</x:v>
+      </x:c>
+      <x:c r="M61" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B63" s="18" t="s">
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="18" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C63" s="19" t="s"/>
-      <x:c r="D63" s="19" t="s"/>
-      <x:c r="E63" s="20" t="s"/>
-      <x:c r="F63" s="20" t="s"/>
-    </x:row>
-    <x:row r="64" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B64" s="21" t="s">
+      <x:c r="C64" s="19" t="s"/>
+      <x:c r="D64" s="19" t="s"/>
+      <x:c r="E64" s="20" t="s"/>
+      <x:c r="F64" s="20" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="21" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C64" s="22" t="s"/>
-      <x:c r="D64" s="22" t="s"/>
-      <x:c r="E64" s="22" t="s"/>
-      <x:c r="F64" s="23" t="s">
+      <x:c r="C65" s="22" t="s"/>
+      <x:c r="D65" s="22" t="s"/>
+      <x:c r="E65" s="22" t="s"/>
+      <x:c r="F65" s="23" t="s">
         <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B65" s="24" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C65" s="25" t="s"/>
-      <x:c r="D65" s="25" t="s"/>
-      <x:c r="E65" s="25" t="s"/>
-      <x:c r="F65" s="26" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:28" ht="18" customHeight="1">
       <x:c r="B66" s="24" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C66" s="25" t="s"/>
       <x:c r="D66" s="25" t="s"/>
       <x:c r="E66" s="25" t="s"/>
       <x:c r="F66" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="18" customHeight="1">
       <x:c r="B67" s="24" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C67" s="25" t="s"/>
       <x:c r="D67" s="25" t="s"/>
@@ -5664,93 +5706,103 @@
     </x:row>
     <x:row r="68" spans="1:28" ht="18" customHeight="1">
       <x:c r="B68" s="24" t="s">
-        <x:v>133</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C68" s="25" t="s"/>
       <x:c r="D68" s="25" t="s"/>
       <x:c r="E68" s="25" t="s"/>
       <x:c r="F68" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="18" customHeight="1">
       <x:c r="B69" s="24" t="s">
-        <x:v>371</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C69" s="25" t="s"/>
       <x:c r="D69" s="25" t="s"/>
       <x:c r="E69" s="25" t="s"/>
       <x:c r="F69" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="18" customHeight="1">
       <x:c r="B70" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C70" s="25" t="s"/>
       <x:c r="D70" s="25" t="s"/>
       <x:c r="E70" s="25" t="s"/>
       <x:c r="F70" s="26" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="18" customHeight="1">
       <x:c r="B71" s="24" t="s">
-        <x:v>761</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C71" s="25" t="s"/>
       <x:c r="D71" s="25" t="s"/>
       <x:c r="E71" s="25" t="s"/>
       <x:c r="F71" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="18" customHeight="1">
       <x:c r="B72" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="C72" s="25" t="s"/>
       <x:c r="D72" s="25" t="s"/>
       <x:c r="E72" s="25" t="s"/>
       <x:c r="F72" s="26" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:28" ht="18" customHeight="1">
       <x:c r="B73" s="24" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="25" t="s"/>
       <x:c r="D73" s="25" t="s"/>
       <x:c r="E73" s="25" t="s"/>
       <x:c r="F73" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:28" ht="18" customHeight="1">
       <x:c r="B74" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C74" s="25" t="s"/>
       <x:c r="D74" s="25" t="s"/>
       <x:c r="E74" s="25" t="s"/>
       <x:c r="F74" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B75" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C75" s="25" t="s"/>
+      <x:c r="D75" s="25" t="s"/>
+      <x:c r="E75" s="25" t="s"/>
+      <x:c r="F75" s="26" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B75" s="27" t="s">
+    <x:row r="76" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B76" s="27" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C75" s="28" t="s"/>
-      <x:c r="D75" s="28" t="s"/>
-      <x:c r="E75" s="28" t="s"/>
-      <x:c r="F75" s="29" t="n">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C76" s="28" t="s"/>
+      <x:c r="D76" s="28" t="s"/>
+      <x:c r="E76" s="28" t="s"/>
+      <x:c r="F76" s="29" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
     <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6673,8 +6725,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B63:F63"/>
-    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B64:F64"/>
     <x:mergeCell ref="B65:E65"/>
     <x:mergeCell ref="B66:E66"/>
     <x:mergeCell ref="B67:E67"/>
@@ -6686,6 +6737,7 @@
     <x:mergeCell ref="B73:E73"/>
     <x:mergeCell ref="B74:E74"/>
     <x:mergeCell ref="B75:E75"/>
+    <x:mergeCell ref="B76:E76"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="907">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="919">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2316,6 +2316,42 @@
     <x:t>1216184</x:t>
   </x:si>
   <x:si>
+    <x:t>Ayala, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0629F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1399-659</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sangali, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0630F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1398-278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VETERANS VILLAGE, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0601G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1397-805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347135</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
   </x:si>
   <x:si>
@@ -2445,6 +2481,18 @@
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216150</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -2469,21 +2517,42 @@
     <x:t>1216152</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0880-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1343-619</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216150</x:t>
-  </x:si>
-  <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0881-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1342-435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS-4878-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0882-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1369-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216163</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -2494,39 +2563,6 @@
   </x:si>
   <x:si>
     <x:t>1216161</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0882-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1369-049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0881-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1342-435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS-4878-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1362-288</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216154</x:t>
   </x:si>
   <x:si>
     <x:t>REY S. BURBURAN</x:t>
@@ -4417,148 +4453,148 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="13" t="s">
-        <x:v>761</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D29" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="13" t="s">
+        <x:v>761</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="s">
         <x:v>762</x:v>
       </x:c>
-      <x:c r="F29" s="13" t="s">
+      <x:c r="G29" s="13" t="s">
         <x:v>763</x:v>
       </x:c>
-      <x:c r="G29" s="13" t="s">
+      <x:c r="H29" s="15">
+        <x:v>46094.3289943287</x:v>
+      </x:c>
+      <x:c r="I29" s="15">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="s">
         <x:v>764</x:v>
       </x:c>
-      <x:c r="H29" s="15">
-        <x:v>46076.3189094676</x:v>
-      </x:c>
-      <x:c r="I29" s="15">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J29" s="14" t="s">
-        <x:v>765</x:v>
-      </x:c>
       <x:c r="K29" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="17">
-        <x:v>46092.1400343403</x:v>
+        <x:v>46107.1436918634</x:v>
       </x:c>
       <x:c r="M29" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B30" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="s">
         <x:v>766</x:v>
       </x:c>
-      <x:c r="C30" s="13" t="s">
-        <x:v>707</x:v>
-      </x:c>
-      <x:c r="D30" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E30" s="13" t="s">
+      <x:c r="G30" s="13" t="s">
         <x:v>767</x:v>
       </x:c>
-      <x:c r="F30" s="13" t="s">
+      <x:c r="H30" s="15">
+        <x:v>46094.3273162269</x:v>
+      </x:c>
+      <x:c r="I30" s="15">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="s">
         <x:v>768</x:v>
       </x:c>
-      <x:c r="G30" s="13" t="s">
-        <x:v>769</x:v>
-      </x:c>
-      <x:c r="H30" s="15">
-        <x:v>46079.2852568981</x:v>
-      </x:c>
-      <x:c r="I30" s="15">
-        <x:v>46079.2852718981</x:v>
-      </x:c>
-      <x:c r="J30" s="14" t="s">
-        <x:v>770</x:v>
-      </x:c>
       <x:c r="K30" s="16" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="17">
-        <x:v>46097.2459243171</x:v>
+        <x:v>46107.1513918519</x:v>
       </x:c>
       <x:c r="M30" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="13" t="s">
-        <x:v>766</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="13" t="s">
-        <x:v>717</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="13" t="s">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="s">
+        <x:v>770</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="s">
         <x:v>771</x:v>
       </x:c>
-      <x:c r="F31" s="13" t="s">
+      <x:c r="H31" s="15">
+        <x:v>46094.3172049306</x:v>
+      </x:c>
+      <x:c r="I31" s="15">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="s">
         <x:v>772</x:v>
       </x:c>
-      <x:c r="G31" s="13" t="s">
-        <x:v>773</x:v>
-      </x:c>
-      <x:c r="H31" s="15">
-        <x:v>46079.2747337153</x:v>
-      </x:c>
-      <x:c r="I31" s="15">
-        <x:v>46079.2747495718</x:v>
-      </x:c>
-      <x:c r="J31" s="14" t="s">
-        <x:v>774</x:v>
-      </x:c>
       <x:c r="K31" s="16" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="17">
-        <x:v>46097.2536368518</x:v>
+        <x:v>46107.1610127431</x:v>
       </x:c>
       <x:c r="M31" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B32" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="13" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="D32" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="13" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="s">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="s">
         <x:v>776</x:v>
       </x:c>
-      <x:c r="F32" s="13" t="s">
+      <x:c r="H32" s="15">
+        <x:v>46076.3189094676</x:v>
+      </x:c>
+      <x:c r="I32" s="15">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="s">
         <x:v>777</x:v>
       </x:c>
-      <x:c r="G32" s="13" t="s">
-        <x:v>778</x:v>
-      </x:c>
-      <x:c r="H32" s="15">
-        <x:v>46076.1792420602</x:v>
-      </x:c>
-      <x:c r="I32" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J32" s="14" t="s">
-        <x:v>779</x:v>
-      </x:c>
       <x:c r="K32" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L32" s="17">
-        <x:v>46090.204281088</x:v>
+        <x:v>46092.1400343403</x:v>
       </x:c>
       <x:c r="M32" s="13" t="s">
         <x:v>28</x:v>
@@ -4566,37 +4602,37 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B33" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="C33" s="13" t="s">
-        <x:v>775</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D33" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E33" s="13" t="s">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="s">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="F33" s="13" t="s">
+      <x:c r="G33" s="13" t="s">
         <x:v>781</x:v>
       </x:c>
-      <x:c r="G33" s="13" t="s">
+      <x:c r="H33" s="15">
+        <x:v>46079.2852568981</x:v>
+      </x:c>
+      <x:c r="I33" s="15">
+        <x:v>46079.2852718981</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="s">
         <x:v>782</x:v>
       </x:c>
-      <x:c r="H33" s="15">
-        <x:v>46072.0333546991</x:v>
-      </x:c>
-      <x:c r="I33" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J33" s="14" t="s">
-        <x:v>783</x:v>
-      </x:c>
       <x:c r="K33" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L33" s="17">
-        <x:v>46090.2584930556</x:v>
+        <x:v>46097.2459243171</x:v>
       </x:c>
       <x:c r="M33" s="13" t="s">
         <x:v>28</x:v>
@@ -4604,37 +4640,37 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B34" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="C34" s="13" t="s">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="s">
         <x:v>784</x:v>
       </x:c>
-      <x:c r="D34" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E34" s="13" t="s">
+      <x:c r="G34" s="13" t="s">
         <x:v>785</x:v>
       </x:c>
-      <x:c r="F34" s="13" t="s">
+      <x:c r="H34" s="15">
+        <x:v>46079.2747337153</x:v>
+      </x:c>
+      <x:c r="I34" s="15">
+        <x:v>46079.2747495718</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="s">
         <x:v>786</x:v>
       </x:c>
-      <x:c r="G34" s="13" t="s">
-        <x:v>787</x:v>
-      </x:c>
-      <x:c r="H34" s="15">
-        <x:v>46071.1677711806</x:v>
-      </x:c>
-      <x:c r="I34" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J34" s="14" t="s">
-        <x:v>788</x:v>
-      </x:c>
       <x:c r="K34" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L34" s="17">
-        <x:v>46091.1948946528</x:v>
+        <x:v>46097.2536368518</x:v>
       </x:c>
       <x:c r="M34" s="13" t="s">
         <x:v>28</x:v>
@@ -4645,34 +4681,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C35" s="13" t="s">
-        <x:v>789</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D35" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="13" t="s">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="s">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="G35" s="13" t="s">
         <x:v>790</x:v>
       </x:c>
-      <x:c r="F35" s="13" t="s">
+      <x:c r="H35" s="15">
+        <x:v>46076.1792420602</x:v>
+      </x:c>
+      <x:c r="I35" s="15">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="s">
         <x:v>791</x:v>
       </x:c>
-      <x:c r="G35" s="13" t="s">
-        <x:v>792</x:v>
-      </x:c>
-      <x:c r="H35" s="15">
-        <x:v>46070.1768476389</x:v>
-      </x:c>
-      <x:c r="I35" s="15">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J35" s="14" t="s">
-        <x:v>793</x:v>
-      </x:c>
       <x:c r="K35" s="16" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L35" s="17">
-        <x:v>46084.1495253588</x:v>
+        <x:v>46090.204281088</x:v>
       </x:c>
       <x:c r="M35" s="13" t="s">
         <x:v>28</x:v>
@@ -4683,34 +4719,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C36" s="13" t="s">
-        <x:v>794</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D36" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="13" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="H36" s="15">
+        <x:v>46072.0333546991</x:v>
+      </x:c>
+      <x:c r="I36" s="15">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J36" s="14" t="s">
         <x:v>795</x:v>
       </x:c>
-      <x:c r="F36" s="13" t="s">
-        <x:v>796</x:v>
-      </x:c>
-      <x:c r="G36" s="13" t="s">
-        <x:v>797</x:v>
-      </x:c>
-      <x:c r="H36" s="15">
-        <x:v>46076.1139638194</x:v>
-      </x:c>
-      <x:c r="I36" s="15">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J36" s="14" t="s">
-        <x:v>798</x:v>
-      </x:c>
       <x:c r="K36" s="16" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L36" s="17">
-        <x:v>46090.1919488889</x:v>
+        <x:v>46090.2584930556</x:v>
       </x:c>
       <x:c r="M36" s="13" t="s">
         <x:v>28</x:v>
@@ -4721,34 +4757,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="13" t="s">
-        <x:v>624</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="D37" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="13" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="s">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="G37" s="13" t="s">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="F37" s="13" t="s">
+      <x:c r="H37" s="15">
+        <x:v>46071.1677711806</x:v>
+      </x:c>
+      <x:c r="I37" s="15">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J37" s="14" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="G37" s="13" t="s">
-        <x:v>801</x:v>
-      </x:c>
-      <x:c r="H37" s="15">
-        <x:v>46071.3305731597</x:v>
-      </x:c>
-      <x:c r="I37" s="15">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J37" s="14" t="s">
-        <x:v>802</x:v>
-      </x:c>
       <x:c r="K37" s="16" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L37" s="17">
-        <x:v>46094.1906452199</x:v>
+        <x:v>46091.1948946528</x:v>
       </x:c>
       <x:c r="M37" s="13" t="s">
         <x:v>28</x:v>
@@ -4759,34 +4795,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="13" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="D38" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="13" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="s">
         <x:v>804</x:v>
       </x:c>
-      <x:c r="F38" s="13" t="s">
+      <x:c r="H38" s="15">
+        <x:v>46070.1768476389</x:v>
+      </x:c>
+      <x:c r="I38" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J38" s="14" t="s">
         <x:v>805</x:v>
       </x:c>
-      <x:c r="G38" s="13" t="s">
-        <x:v>806</x:v>
-      </x:c>
-      <x:c r="H38" s="15">
-        <x:v>46077.2598841551</x:v>
-      </x:c>
-      <x:c r="I38" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J38" s="14" t="s">
-        <x:v>807</x:v>
-      </x:c>
       <x:c r="K38" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L38" s="17">
-        <x:v>46090.2758708681</x:v>
+        <x:v>46084.1495253588</x:v>
       </x:c>
       <x:c r="M38" s="13" t="s">
         <x:v>28</x:v>
@@ -4797,34 +4833,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="13" t="s">
-        <x:v>803</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="D39" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="13" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="F39" s="13" t="s">
         <x:v>808</x:v>
       </x:c>
-      <x:c r="F39" s="13" t="s">
+      <x:c r="G39" s="13" t="s">
         <x:v>809</x:v>
       </x:c>
-      <x:c r="G39" s="13" t="s">
+      <x:c r="H39" s="15">
+        <x:v>46076.1139638194</x:v>
+      </x:c>
+      <x:c r="I39" s="15">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J39" s="14" t="s">
         <x:v>810</x:v>
       </x:c>
-      <x:c r="H39" s="15">
-        <x:v>46072.1089512963</x:v>
-      </x:c>
-      <x:c r="I39" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J39" s="14" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="K39" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L39" s="17">
-        <x:v>46090.2365117824</x:v>
+        <x:v>46090.1919488889</x:v>
       </x:c>
       <x:c r="M39" s="13" t="s">
         <x:v>28</x:v>
@@ -4835,34 +4871,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="13" t="s">
-        <x:v>803</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D40" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="13" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="s">
         <x:v>812</x:v>
       </x:c>
-      <x:c r="F40" s="13" t="s">
+      <x:c r="G40" s="13" t="s">
         <x:v>813</x:v>
       </x:c>
-      <x:c r="G40" s="13" t="s">
+      <x:c r="H40" s="15">
+        <x:v>46071.3305731597</x:v>
+      </x:c>
+      <x:c r="I40" s="15">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J40" s="14" t="s">
         <x:v>814</x:v>
       </x:c>
-      <x:c r="H40" s="15">
-        <x:v>46072.0792950116</x:v>
-      </x:c>
-      <x:c r="I40" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J40" s="14" t="s">
-        <x:v>815</x:v>
-      </x:c>
       <x:c r="K40" s="16" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L40" s="17">
-        <x:v>46090.220792662</x:v>
+        <x:v>46094.1906452199</x:v>
       </x:c>
       <x:c r="M40" s="13" t="s">
         <x:v>28</x:v>
@@ -4873,34 +4909,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="D41" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="13" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="F41" s="13" t="s">
         <x:v>817</x:v>
       </x:c>
-      <x:c r="F41" s="13" t="s">
+      <x:c r="G41" s="13" t="s">
         <x:v>818</x:v>
       </x:c>
-      <x:c r="G41" s="13" t="s">
+      <x:c r="H41" s="15">
+        <x:v>46072.0792950116</x:v>
+      </x:c>
+      <x:c r="I41" s="15">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J41" s="14" t="s">
         <x:v>819</x:v>
-      </x:c>
-      <x:c r="H41" s="15">
-        <x:v>46077.4722378472</x:v>
-      </x:c>
-      <x:c r="I41" s="15">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J41" s="14" t="s">
-        <x:v>820</x:v>
       </x:c>
       <x:c r="K41" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L41" s="17">
-        <x:v>46090.2963156019</x:v>
+        <x:v>46090.220792662</x:v>
       </x:c>
       <x:c r="M41" s="13" t="s">
         <x:v>28</x:v>
@@ -4911,34 +4947,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="D42" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="13" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="s">
         <x:v>821</x:v>
       </x:c>
-      <x:c r="F42" s="13" t="s">
+      <x:c r="G42" s="13" t="s">
         <x:v>822</x:v>
       </x:c>
-      <x:c r="G42" s="13" t="s">
-        <x:v>823</x:v>
-      </x:c>
       <x:c r="H42" s="15">
-        <x:v>46077.5191885417</x:v>
+        <x:v>46077.2598841551</x:v>
       </x:c>
       <x:c r="I42" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J42" s="14" t="s">
-        <x:v>824</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="K42" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L42" s="17">
-        <x:v>46090.3155018056</x:v>
+        <x:v>46090.2758708681</x:v>
       </x:c>
       <x:c r="M42" s="13" t="s">
         <x:v>28</x:v>
@@ -4949,34 +4985,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C43" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="D43" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="13" t="s">
+        <x:v>824</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="s">
         <x:v>825</x:v>
       </x:c>
-      <x:c r="F43" s="13" t="s">
+      <x:c r="G43" s="13" t="s">
         <x:v>826</x:v>
       </x:c>
-      <x:c r="G43" s="13" t="s">
-        <x:v>827</x:v>
-      </x:c>
       <x:c r="H43" s="15">
-        <x:v>46072.0497342708</x:v>
+        <x:v>46072.1089512963</x:v>
       </x:c>
       <x:c r="I43" s="15">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J43" s="14" t="s">
-        <x:v>828</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="K43" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L43" s="17">
-        <x:v>46090.2102464352</x:v>
+        <x:v>46090.2365117824</x:v>
       </x:c>
       <x:c r="M43" s="13" t="s">
         <x:v>28</x:v>
@@ -4987,34 +5023,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C44" s="13" t="s">
-        <x:v>816</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="D44" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="13" t="s">
-        <x:v>812</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="F44" s="13" t="s">
-        <x:v>829</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="G44" s="13" t="s">
-        <x:v>830</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="H44" s="15">
-        <x:v>46077.2024189931</x:v>
+        <x:v>46072.0497342708</x:v>
       </x:c>
       <x:c r="I44" s="15">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J44" s="14" t="s">
-        <x:v>831</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="K44" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L44" s="17">
-        <x:v>46090.2496018056</x:v>
+        <x:v>46090.2102464352</x:v>
       </x:c>
       <x:c r="M44" s="13" t="s">
         <x:v>28</x:v>
@@ -5025,34 +5061,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C45" s="13" t="s">
-        <x:v>832</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="D45" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="13" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="F45" s="13" t="s">
         <x:v>833</x:v>
       </x:c>
-      <x:c r="F45" s="13" t="s">
+      <x:c r="G45" s="13" t="s">
         <x:v>834</x:v>
       </x:c>
-      <x:c r="G45" s="13" t="s">
+      <x:c r="H45" s="15">
+        <x:v>46077.2024189931</x:v>
+      </x:c>
+      <x:c r="I45" s="15">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J45" s="14" t="s">
         <x:v>835</x:v>
-      </x:c>
-      <x:c r="H45" s="15">
-        <x:v>46071.2072683796</x:v>
-      </x:c>
-      <x:c r="I45" s="15">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J45" s="14" t="s">
-        <x:v>836</x:v>
       </x:c>
       <x:c r="K45" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L45" s="17">
-        <x:v>46090.0616673032</x:v>
+        <x:v>46090.2496018056</x:v>
       </x:c>
       <x:c r="M45" s="13" t="s">
         <x:v>28</x:v>
@@ -5063,13 +5099,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C46" s="13" t="s">
-        <x:v>832</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="D46" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="13" t="s">
-        <x:v>812</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="F46" s="13" t="s">
         <x:v>837</x:v>
@@ -5078,7 +5114,7 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="H46" s="15">
-        <x:v>46071.2285509838</x:v>
+        <x:v>46077.5191885417</x:v>
       </x:c>
       <x:c r="I46" s="15">
         <x:v>46058</x:v>
@@ -5090,7 +5126,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L46" s="17">
-        <x:v>46090.0772934491</x:v>
+        <x:v>46090.3155018056</x:v>
       </x:c>
       <x:c r="M46" s="13" t="s">
         <x:v>28</x:v>
@@ -5101,7 +5137,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C47" s="13" t="s">
-        <x:v>320</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="D47" s="14" t="s">
         <x:v>16</x:v>
@@ -5116,19 +5152,19 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="H47" s="15">
-        <x:v>46079.0151889352</x:v>
+        <x:v>46077.4722378472</x:v>
       </x:c>
       <x:c r="I47" s="15">
-        <x:v>45602</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J47" s="14" t="s">
         <x:v>843</x:v>
       </x:c>
       <x:c r="K47" s="16" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L47" s="17">
-        <x:v>46093.1514429977</x:v>
+        <x:v>46090.2963156019</x:v>
       </x:c>
       <x:c r="M47" s="13" t="s">
         <x:v>28</x:v>
@@ -5139,34 +5175,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C48" s="13" t="s">
-        <x:v>320</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="D48" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="13" t="s">
-        <x:v>321</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="F48" s="13" t="s">
-        <x:v>844</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="G48" s="13" t="s">
-        <x:v>845</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="H48" s="15">
-        <x:v>45988.189350544</x:v>
+        <x:v>46071.2072683796</x:v>
       </x:c>
       <x:c r="I48" s="15">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J48" s="14" t="s">
-        <x:v>846</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="K48" s="16" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L48" s="17">
-        <x:v>46093.1383928935</x:v>
+        <x:v>46090.0616673032</x:v>
       </x:c>
       <x:c r="M48" s="13" t="s">
         <x:v>28</x:v>
@@ -5174,14 +5210,16 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C49" s="13" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="D49" s="14" t="s"/>
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E49" s="13" t="s">
-        <x:v>848</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="F49" s="13" t="s">
         <x:v>849</x:v>
@@ -5190,19 +5228,19 @@
         <x:v>850</x:v>
       </x:c>
       <x:c r="H49" s="15">
-        <x:v>46090.2854096643</x:v>
+        <x:v>46071.2285509838</x:v>
       </x:c>
       <x:c r="I49" s="15">
-        <x:v>46090.2854287153</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J49" s="14" t="s">
-        <x:v>850</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="K49" s="16" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L49" s="17">
-        <x:v>46094.0865837153</x:v>
+        <x:v>46090.0772934491</x:v>
       </x:c>
       <x:c r="M49" s="13" t="s">
         <x:v>28</x:v>
@@ -5210,12 +5248,14 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B50" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C50" s="13" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="D50" s="14" t="s"/>
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E50" s="13" t="s">
         <x:v>852</x:v>
       </x:c>
@@ -5226,19 +5266,19 @@
         <x:v>854</x:v>
       </x:c>
       <x:c r="H50" s="15">
-        <x:v>46090.2541037731</x:v>
+        <x:v>46079.0151889352</x:v>
       </x:c>
       <x:c r="I50" s="15">
-        <x:v>46090.2541222106</x:v>
+        <x:v>45602</x:v>
       </x:c>
       <x:c r="J50" s="14" t="s">
         <x:v>855</x:v>
       </x:c>
       <x:c r="K50" s="16" t="n">
-        <x:v>426</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L50" s="17">
-        <x:v>46094.0819034491</x:v>
+        <x:v>46093.1514429977</x:v>
       </x:c>
       <x:c r="M50" s="13" t="s">
         <x:v>28</x:v>
@@ -5246,35 +5286,37 @@
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B51" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C51" s="13" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F51" s="13" t="s">
         <x:v>856</x:v>
       </x:c>
-      <x:c r="D51" s="14" t="s"/>
-      <x:c r="E51" s="13" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="F51" s="13" t="s">
+      <x:c r="G51" s="13" t="s">
         <x:v>857</x:v>
       </x:c>
-      <x:c r="G51" s="13" t="s">
+      <x:c r="H51" s="15">
+        <x:v>45988.189350544</x:v>
+      </x:c>
+      <x:c r="I51" s="15">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J51" s="14" t="s">
         <x:v>858</x:v>
       </x:c>
-      <x:c r="H51" s="15">
-        <x:v>46090.2349194444</x:v>
-      </x:c>
-      <x:c r="I51" s="15">
-        <x:v>46090.2349374884</x:v>
-      </x:c>
-      <x:c r="J51" s="14" t="s">
-        <x:v>859</x:v>
-      </x:c>
       <x:c r="K51" s="16" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L51" s="17">
-        <x:v>46094.093939213</x:v>
+        <x:v>46093.1383928935</x:v>
       </x:c>
       <x:c r="M51" s="13" t="s">
         <x:v>28</x:v>
@@ -5282,37 +5324,35 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B52" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C52" s="13" t="s">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="s"/>
+      <x:c r="E52" s="13" t="s">
         <x:v>860</x:v>
       </x:c>
-      <x:c r="D52" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E52" s="13" t="s">
+      <x:c r="F52" s="13" t="s">
         <x:v>861</x:v>
       </x:c>
-      <x:c r="F52" s="13" t="s">
+      <x:c r="G52" s="13" t="s">
         <x:v>862</x:v>
       </x:c>
-      <x:c r="G52" s="13" t="s">
-        <x:v>863</x:v>
-      </x:c>
       <x:c r="H52" s="15">
-        <x:v>46073.0262962616</x:v>
+        <x:v>46090.2854096643</x:v>
       </x:c>
       <x:c r="I52" s="15">
-        <x:v>46042</x:v>
+        <x:v>46090.2854287153</x:v>
       </x:c>
       <x:c r="J52" s="14" t="s">
-        <x:v>864</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="K52" s="16" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L52" s="17">
-        <x:v>46090.2670310069</x:v>
+        <x:v>46094.0865837153</x:v>
       </x:c>
       <x:c r="M52" s="13" t="s">
         <x:v>28</x:v>
@@ -5320,37 +5360,35 @@
     </x:row>
     <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B53" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C53" s="13" t="s">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="s"/>
+      <x:c r="E53" s="13" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="F53" s="13" t="s">
         <x:v>865</x:v>
       </x:c>
-      <x:c r="D53" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E53" s="13" t="s">
+      <x:c r="G53" s="13" t="s">
         <x:v>866</x:v>
       </x:c>
-      <x:c r="F53" s="13" t="s">
+      <x:c r="H53" s="15">
+        <x:v>46090.2541037731</x:v>
+      </x:c>
+      <x:c r="I53" s="15">
+        <x:v>46090.2541222106</x:v>
+      </x:c>
+      <x:c r="J53" s="14" t="s">
         <x:v>867</x:v>
       </x:c>
-      <x:c r="G53" s="13" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="H53" s="15">
-        <x:v>46077.2103691435</x:v>
-      </x:c>
-      <x:c r="I53" s="15">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J53" s="14" t="s">
-        <x:v>869</x:v>
-      </x:c>
       <x:c r="K53" s="16" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L53" s="17">
-        <x:v>46090.253629537</x:v>
+        <x:v>46094.0819034491</x:v>
       </x:c>
       <x:c r="M53" s="13" t="s">
         <x:v>28</x:v>
@@ -5358,37 +5396,35 @@
     </x:row>
     <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B54" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C54" s="13" t="s">
+        <x:v>868</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="s"/>
+      <x:c r="E54" s="13" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="F54" s="13" t="s">
+        <x:v>869</x:v>
+      </x:c>
+      <x:c r="G54" s="13" t="s">
         <x:v>870</x:v>
       </x:c>
-      <x:c r="D54" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E54" s="13" t="s">
+      <x:c r="H54" s="15">
+        <x:v>46090.2349194444</x:v>
+      </x:c>
+      <x:c r="I54" s="15">
+        <x:v>46090.2349374884</x:v>
+      </x:c>
+      <x:c r="J54" s="14" t="s">
         <x:v>871</x:v>
       </x:c>
-      <x:c r="F54" s="13" t="s">
-        <x:v>872</x:v>
-      </x:c>
-      <x:c r="G54" s="13" t="s">
-        <x:v>873</x:v>
-      </x:c>
-      <x:c r="H54" s="15">
-        <x:v>46073.0478536458</x:v>
-      </x:c>
-      <x:c r="I54" s="15">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J54" s="14" t="s">
-        <x:v>874</x:v>
-      </x:c>
       <x:c r="K54" s="16" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L54" s="17">
-        <x:v>46090.2431909954</x:v>
+        <x:v>46094.093939213</x:v>
       </x:c>
       <x:c r="M54" s="13" t="s">
         <x:v>28</x:v>
@@ -5399,34 +5435,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C55" s="13" t="s">
-        <x:v>875</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="D55" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="13" t="s">
-        <x:v>804</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="F55" s="13" t="s">
+        <x:v>874</x:v>
+      </x:c>
+      <x:c r="G55" s="13" t="s">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="H55" s="15">
+        <x:v>46073.0262962616</x:v>
+      </x:c>
+      <x:c r="I55" s="15">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J55" s="14" t="s">
         <x:v>876</x:v>
       </x:c>
-      <x:c r="G55" s="13" t="s">
-        <x:v>877</x:v>
-      </x:c>
-      <x:c r="H55" s="15">
-        <x:v>46073.10951125</x:v>
-      </x:c>
-      <x:c r="I55" s="15">
-        <x:v>45824</x:v>
-      </x:c>
-      <x:c r="J55" s="14" t="s">
-        <x:v>878</x:v>
-      </x:c>
       <x:c r="K55" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L55" s="17">
-        <x:v>46091.1210900116</x:v>
+        <x:v>46090.2670310069</x:v>
       </x:c>
       <x:c r="M55" s="13" t="s">
         <x:v>28</x:v>
@@ -5437,34 +5473,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="13" t="s">
-        <x:v>879</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="D56" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="13" t="s">
-        <x:v>804</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="F56" s="13" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="G56" s="13" t="s">
         <x:v>880</x:v>
       </x:c>
-      <x:c r="G56" s="13" t="s">
+      <x:c r="H56" s="15">
+        <x:v>46077.2103691435</x:v>
+      </x:c>
+      <x:c r="I56" s="15">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J56" s="14" t="s">
         <x:v>881</x:v>
-      </x:c>
-      <x:c r="H56" s="15">
-        <x:v>46073.0611031366</x:v>
-      </x:c>
-      <x:c r="I56" s="15">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="J56" s="14" t="s">
-        <x:v>882</x:v>
       </x:c>
       <x:c r="K56" s="16" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L56" s="17">
-        <x:v>46090.2266513079</x:v>
+        <x:v>46090.253629537</x:v>
       </x:c>
       <x:c r="M56" s="13" t="s">
         <x:v>28</x:v>
@@ -5475,34 +5511,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="13" t="s">
-        <x:v>883</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="D57" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="13" t="s">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="F57" s="13" t="s">
         <x:v>884</x:v>
       </x:c>
-      <x:c r="F57" s="13" t="s">
+      <x:c r="G57" s="13" t="s">
         <x:v>885</x:v>
       </x:c>
-      <x:c r="G57" s="13" t="s">
+      <x:c r="H57" s="15">
+        <x:v>46073.0478536458</x:v>
+      </x:c>
+      <x:c r="I57" s="15">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J57" s="14" t="s">
         <x:v>886</x:v>
       </x:c>
-      <x:c r="H57" s="15">
-        <x:v>46077.2683575231</x:v>
-      </x:c>
-      <x:c r="I57" s="15">
-        <x:v>45748</x:v>
-      </x:c>
-      <x:c r="J57" s="14" t="s">
-        <x:v>887</x:v>
-      </x:c>
       <x:c r="K57" s="16" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L57" s="17">
-        <x:v>46090.2806125347</x:v>
+        <x:v>46090.2431909954</x:v>
       </x:c>
       <x:c r="M57" s="13" t="s">
         <x:v>28</x:v>
@@ -5513,34 +5549,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="13" t="s">
-        <x:v>888</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="D58" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="13" t="s">
-        <x:v>804</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="F58" s="13" t="s">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="G58" s="13" t="s">
         <x:v>889</x:v>
       </x:c>
-      <x:c r="G58" s="13" t="s">
-        <x:v>890</x:v>
-      </x:c>
       <x:c r="H58" s="15">
-        <x:v>46073.0763545833</x:v>
+        <x:v>46073.10951125</x:v>
       </x:c>
       <x:c r="I58" s="15">
         <x:v>45824</x:v>
       </x:c>
       <x:c r="J58" s="14" t="s">
-        <x:v>891</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="K58" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L58" s="17">
-        <x:v>46090.2162962268</x:v>
+        <x:v>46091.1210900116</x:v>
       </x:c>
       <x:c r="M58" s="13" t="s">
         <x:v>28</x:v>
@@ -5551,34 +5587,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C59" s="13" t="s">
-        <x:v>892</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="D59" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="13" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="F59" s="13" t="s">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c r="G59" s="13" t="s">
         <x:v>893</x:v>
       </x:c>
-      <x:c r="F59" s="13" t="s">
+      <x:c r="H59" s="15">
+        <x:v>46073.0611031366</x:v>
+      </x:c>
+      <x:c r="I59" s="15">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="J59" s="14" t="s">
         <x:v>894</x:v>
       </x:c>
-      <x:c r="G59" s="13" t="s">
-        <x:v>895</x:v>
-      </x:c>
-      <x:c r="H59" s="15">
-        <x:v>46077.1834319213</x:v>
-      </x:c>
-      <x:c r="I59" s="15">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J59" s="14" t="s">
-        <x:v>896</x:v>
-      </x:c>
       <x:c r="K59" s="16" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L59" s="17">
-        <x:v>46091.2388780324</x:v>
+        <x:v>46090.2266513079</x:v>
       </x:c>
       <x:c r="M59" s="13" t="s">
         <x:v>28</x:v>
@@ -5589,34 +5625,34 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="13" t="s">
-        <x:v>897</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="D60" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="13" t="s">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="F60" s="13" t="s">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="G60" s="13" t="s">
         <x:v>898</x:v>
       </x:c>
-      <x:c r="F60" s="13" t="s">
-        <x:v>899</x:v>
-      </x:c>
-      <x:c r="G60" s="13" t="s">
-        <x:v>900</x:v>
-      </x:c>
       <x:c r="H60" s="15">
-        <x:v>46071.2853697569</x:v>
+        <x:v>46077.2683575231</x:v>
       </x:c>
       <x:c r="I60" s="15">
         <x:v>45748</x:v>
       </x:c>
       <x:c r="J60" s="14" t="s">
-        <x:v>901</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="K60" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L60" s="17">
-        <x:v>46094.1777229282</x:v>
+        <x:v>46090.2806125347</x:v>
       </x:c>
       <x:c r="M60" s="13" t="s">
         <x:v>28</x:v>
@@ -5627,185 +5663,296 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C61" s="13" t="s">
-        <x:v>902</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="D61" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="13" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="F61" s="13" t="s">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="G61" s="13" t="s">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="H61" s="15">
+        <x:v>46073.0763545833</x:v>
+      </x:c>
+      <x:c r="I61" s="15">
+        <x:v>45824</x:v>
+      </x:c>
+      <x:c r="J61" s="14" t="s">
         <x:v>903</x:v>
       </x:c>
-      <x:c r="F61" s="13" t="s">
-        <x:v>904</x:v>
-      </x:c>
-      <x:c r="G61" s="13" t="s">
-        <x:v>905</x:v>
-      </x:c>
-      <x:c r="H61" s="15">
-        <x:v>46090.3681394907</x:v>
-      </x:c>
-      <x:c r="I61" s="15">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J61" s="14" t="s">
-        <x:v>906</x:v>
-      </x:c>
       <x:c r="K61" s="16" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L61" s="17">
-        <x:v>46094.1826630093</x:v>
+        <x:v>46090.2162962268</x:v>
       </x:c>
       <x:c r="M61" s="13" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="18" t="s">
+    <x:row r="62" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B62" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C62" s="13" t="s">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E62" s="13" t="s">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="F62" s="13" t="s">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="G62" s="13" t="s">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="H62" s="15">
+        <x:v>46077.1834319213</x:v>
+      </x:c>
+      <x:c r="I62" s="15">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J62" s="14" t="s">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="K62" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L62" s="17">
+        <x:v>46091.2388780324</x:v>
+      </x:c>
+      <x:c r="M62" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B63" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C63" s="13" t="s">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E63" s="13" t="s">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="F63" s="13" t="s">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="G63" s="13" t="s">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="H63" s="15">
+        <x:v>46071.2853697569</x:v>
+      </x:c>
+      <x:c r="I63" s="15">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J63" s="14" t="s">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="K63" s="16" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L63" s="17">
+        <x:v>46094.1777229282</x:v>
+      </x:c>
+      <x:c r="M63" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B64" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C64" s="13" t="s">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E64" s="13" t="s">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="F64" s="13" t="s">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="G64" s="13" t="s">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="H64" s="15">
+        <x:v>46090.3681394907</x:v>
+      </x:c>
+      <x:c r="I64" s="15">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J64" s="14" t="s">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="K64" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L64" s="17">
+        <x:v>46094.1826630093</x:v>
+      </x:c>
+      <x:c r="M64" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B67" s="18" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C64" s="19" t="s"/>
-      <x:c r="D64" s="19" t="s"/>
-      <x:c r="E64" s="20" t="s"/>
-      <x:c r="F64" s="20" t="s"/>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B65" s="21" t="s">
+      <x:c r="C67" s="19" t="s"/>
+      <x:c r="D67" s="19" t="s"/>
+      <x:c r="E67" s="20" t="s"/>
+      <x:c r="F67" s="20" t="s"/>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B68" s="21" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C65" s="22" t="s"/>
-      <x:c r="D65" s="22" t="s"/>
-      <x:c r="E65" s="22" t="s"/>
-      <x:c r="F65" s="23" t="s">
+      <x:c r="C68" s="22" t="s"/>
+      <x:c r="D68" s="22" t="s"/>
+      <x:c r="E68" s="22" t="s"/>
+      <x:c r="F68" s="23" t="s">
         <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="24" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C66" s="25" t="s"/>
-      <x:c r="D66" s="25" t="s"/>
-      <x:c r="E66" s="25" t="s"/>
-      <x:c r="F66" s="26" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="24" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C67" s="25" t="s"/>
-      <x:c r="D67" s="25" t="s"/>
-      <x:c r="E67" s="25" t="s"/>
-      <x:c r="F67" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="24" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C68" s="25" t="s"/>
-      <x:c r="D68" s="25" t="s"/>
-      <x:c r="E68" s="25" t="s"/>
-      <x:c r="F68" s="26" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="18" customHeight="1">
       <x:c r="B69" s="24" t="s">
-        <x:v>133</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C69" s="25" t="s"/>
       <x:c r="D69" s="25" t="s"/>
       <x:c r="E69" s="25" t="s"/>
       <x:c r="F69" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="18" customHeight="1">
       <x:c r="B70" s="24" t="s">
-        <x:v>371</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C70" s="25" t="s"/>
       <x:c r="D70" s="25" t="s"/>
       <x:c r="E70" s="25" t="s"/>
       <x:c r="F70" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="18" customHeight="1">
       <x:c r="B71" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C71" s="25" t="s"/>
       <x:c r="D71" s="25" t="s"/>
       <x:c r="E71" s="25" t="s"/>
       <x:c r="F71" s="26" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="18" customHeight="1">
       <x:c r="B72" s="24" t="s">
-        <x:v>766</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C72" s="25" t="s"/>
       <x:c r="D72" s="25" t="s"/>
       <x:c r="E72" s="25" t="s"/>
       <x:c r="F72" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:28" ht="18" customHeight="1">
       <x:c r="B73" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C73" s="25" t="s"/>
       <x:c r="D73" s="25" t="s"/>
       <x:c r="E73" s="25" t="s"/>
       <x:c r="F73" s="26" t="n">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:28" ht="18" customHeight="1">
       <x:c r="B74" s="24" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="25" t="s"/>
       <x:c r="D74" s="25" t="s"/>
       <x:c r="E74" s="25" t="s"/>
       <x:c r="F74" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:28" ht="18" customHeight="1">
       <x:c r="B75" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="C75" s="25" t="s"/>
       <x:c r="D75" s="25" t="s"/>
       <x:c r="E75" s="25" t="s"/>
       <x:c r="F75" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B76" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C76" s="25" t="s"/>
+      <x:c r="D76" s="25" t="s"/>
+      <x:c r="E76" s="25" t="s"/>
+      <x:c r="F76" s="26" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B77" s="24" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C77" s="25" t="s"/>
+      <x:c r="D77" s="25" t="s"/>
+      <x:c r="E77" s="25" t="s"/>
+      <x:c r="F77" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B78" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C78" s="25" t="s"/>
+      <x:c r="D78" s="25" t="s"/>
+      <x:c r="E78" s="25" t="s"/>
+      <x:c r="F78" s="26" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B76" s="27" t="s">
+    <x:row r="79" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B79" s="27" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C76" s="28" t="s"/>
-      <x:c r="D76" s="28" t="s"/>
-      <x:c r="E76" s="28" t="s"/>
-      <x:c r="F76" s="29" t="n">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C79" s="28" t="s"/>
+      <x:c r="D79" s="28" t="s"/>
+      <x:c r="E79" s="28" t="s"/>
+      <x:c r="F79" s="29" t="n">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
     <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6725,10 +6872,7 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B64:F64"/>
-    <x:mergeCell ref="B65:E65"/>
-    <x:mergeCell ref="B66:E66"/>
-    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B67:F67"/>
     <x:mergeCell ref="B68:E68"/>
     <x:mergeCell ref="B69:E69"/>
     <x:mergeCell ref="B70:E70"/>
@@ -6738,6 +6882,9 @@
     <x:mergeCell ref="B74:E74"/>
     <x:mergeCell ref="B75:E75"/>
     <x:mergeCell ref="B76:E76"/>
+    <x:mergeCell ref="B77:E77"/>
+    <x:mergeCell ref="B78:E78"/>
+    <x:mergeCell ref="B79:E79"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -3609,7 +3609,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -3649,7 +3649,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>61</x:v>
@@ -3688,7 +3688,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -3726,7 +3726,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -3764,7 +3764,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -3802,7 +3802,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -3840,7 +3840,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -3878,7 +3878,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>78</x:v>
       </x:c>
@@ -3916,7 +3916,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -3954,7 +3954,7 @@
         <x:v>507</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -3992,7 +3992,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>133</x:v>
       </x:c>
@@ -4030,7 +4030,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -4068,7 +4068,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -4106,7 +4106,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -4144,7 +4144,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -4182,7 +4182,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -4220,7 +4220,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4258,7 +4258,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4296,7 +4296,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4334,7 +4334,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4372,7 +4372,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4410,7 +4410,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4448,7 +4448,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4486,7 +4486,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4524,7 +4524,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4562,7 +4562,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -4600,7 +4600,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="13" t="s">
         <x:v>778</x:v>
       </x:c>
@@ -4638,7 +4638,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="13" t="s">
         <x:v>778</x:v>
       </x:c>
@@ -4676,7 +4676,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4714,7 +4714,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4752,7 +4752,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4790,7 +4790,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4828,7 +4828,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4866,7 +4866,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4904,7 +4904,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4942,7 +4942,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -4980,7 +4980,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5018,7 +5018,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5056,7 +5056,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5094,7 +5094,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
       <x:c r="B46" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5132,7 +5132,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
       <x:c r="B47" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5170,7 +5170,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
       <x:c r="B48" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5208,7 +5208,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
       <x:c r="B49" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5246,7 +5246,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
       <x:c r="B50" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5284,7 +5284,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
       <x:c r="B51" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -5322,7 +5322,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
       <x:c r="B52" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -5358,7 +5358,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
       <x:c r="B53" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -5394,7 +5394,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
       <x:c r="B54" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -5430,7 +5430,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
       <x:c r="B55" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5468,7 +5468,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
       <x:c r="B56" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5506,7 +5506,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
       <x:c r="B57" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5544,7 +5544,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5582,7 +5582,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5620,7 +5620,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="60" spans="1:28" ht="30" customHeight="1">
       <x:c r="B60" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5658,7 +5658,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="61" spans="1:28" ht="30" customHeight="1">
       <x:c r="B61" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5696,7 +5696,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
       <x:c r="B62" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5734,7 +5734,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="63" spans="1:28" ht="30" customHeight="1">
       <x:c r="B63" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -5772,7 +5772,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
       <x:c r="B64" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -7015,7 +7015,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -7055,7 +7055,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
@@ -7094,7 +7094,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -7132,7 +7132,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -7170,7 +7170,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -7208,7 +7208,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -7244,7 +7244,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -8472,7 +8472,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -8512,7 +8512,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>54</x:v>
@@ -8551,7 +8551,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -8589,7 +8589,7 @@
         <x:v>67</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -8627,7 +8627,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -8665,7 +8665,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>78</x:v>
       </x:c>
@@ -8703,7 +8703,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -8741,7 +8741,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -8779,7 +8779,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>95</x:v>
       </x:c>
@@ -8815,7 +8815,7 @@
         <x:v>67</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>101</x:v>
       </x:c>
@@ -8853,7 +8853,7 @@
         <x:v>67</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>105</x:v>
       </x:c>
@@ -8891,7 +8891,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>105</x:v>
       </x:c>
@@ -8929,7 +8929,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>116</x:v>
       </x:c>
@@ -8967,7 +8967,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>122</x:v>
       </x:c>
@@ -9005,7 +9005,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>122</x:v>
       </x:c>
@@ -9043,7 +9043,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="13" t="s">
         <x:v>133</x:v>
       </x:c>
@@ -9081,7 +9081,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -9119,7 +9119,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -9157,7 +9157,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="13" t="s">
         <x:v>144</x:v>
       </x:c>
@@ -9195,7 +9195,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="13" t="s">
         <x:v>144</x:v>
       </x:c>
@@ -9233,7 +9233,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="13" t="s">
         <x:v>154</x:v>
       </x:c>
@@ -9271,7 +9271,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9309,7 +9309,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9347,7 +9347,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9385,7 +9385,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9423,7 +9423,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9461,7 +9461,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9499,7 +9499,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -9537,7 +9537,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="13" t="s">
         <x:v>194</x:v>
       </x:c>
@@ -9575,7 +9575,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -10912,7 +10912,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -10952,7 +10952,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>204</x:v>
@@ -10991,7 +10991,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -11029,7 +11029,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -11067,7 +11067,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -11105,7 +11105,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>105</x:v>
       </x:c>
@@ -11143,7 +11143,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>230</x:v>
       </x:c>
@@ -11181,7 +11181,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -11219,7 +11219,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -11257,7 +11257,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -11295,7 +11295,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -11333,7 +11333,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -11371,7 +11371,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -11409,7 +11409,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -11447,7 +11447,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -11485,7 +11485,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -11523,7 +11523,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -11559,7 +11559,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="13" t="s">
         <x:v>194</x:v>
       </x:c>
@@ -11597,7 +11597,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -11635,7 +11635,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -11673,7 +11673,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -12953,7 +12953,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -12993,7 +12993,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>61</x:v>
@@ -13032,7 +13032,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -13070,7 +13070,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>144</x:v>
       </x:c>
@@ -13108,7 +13108,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -13144,7 +13144,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -13182,7 +13182,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -13220,7 +13220,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -13256,7 +13256,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -13292,7 +13292,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -14539,7 +14539,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -14579,7 +14579,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>346</x:v>
@@ -14616,7 +14616,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -14654,7 +14654,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -14692,7 +14692,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -14730,7 +14730,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -14768,7 +14768,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>371</x:v>
       </x:c>
@@ -14806,7 +14806,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -14844,7 +14844,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -14882,7 +14882,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -14920,7 +14920,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -14958,7 +14958,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>396</x:v>
       </x:c>
@@ -14996,7 +14996,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>396</x:v>
       </x:c>
@@ -15034,7 +15034,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15072,7 +15072,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15110,7 +15110,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15148,7 +15148,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15186,7 +15186,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15224,7 +15224,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -15262,7 +15262,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -15298,7 +15298,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -15334,7 +15334,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -15372,7 +15372,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -16639,7 +16639,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -16679,7 +16679,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>204</x:v>
@@ -16718,7 +16718,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -16756,7 +16756,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -16794,7 +16794,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -16832,7 +16832,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -16870,7 +16870,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -16908,7 +16908,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -16946,7 +16946,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -16984,7 +16984,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -17022,7 +17022,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -18246,7 +18246,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -18286,7 +18286,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>501</x:v>
@@ -18323,7 +18323,7 @@
         <x:v>507</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -18361,7 +18361,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>133</x:v>
       </x:c>
@@ -18399,7 +18399,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -18437,7 +18437,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -18475,7 +18475,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -18513,7 +18513,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -18551,7 +18551,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -18589,7 +18589,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -18627,7 +18627,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -18665,7 +18665,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -18701,7 +18701,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -18739,7 +18739,7 @@
         <x:v>518</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -18777,7 +18777,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -20030,7 +20030,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -20070,7 +20070,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>568</x:v>
@@ -20109,7 +20109,7 @@
         <x:v>507</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -20147,7 +20147,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -20185,7 +20185,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -20223,7 +20223,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -20261,7 +20261,7 @@
         <x:v>507</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -20299,7 +20299,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -20337,7 +20337,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>154</x:v>
       </x:c>
@@ -20375,7 +20375,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20413,7 +20413,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20451,7 +20451,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20489,7 +20489,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20527,7 +20527,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20565,7 +20565,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20603,7 +20603,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20641,7 +20641,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20679,7 +20679,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20717,7 +20717,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -20755,7 +20755,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="13" t="s">
         <x:v>44</x:v>
       </x:c>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -15,6 +15,7 @@
     <x:sheet name="January 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="February 2026" sheetId="14" r:id="rId14"/>
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
+    <x:sheet name="April 2026" sheetId="16" r:id="rId16"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="910">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="920">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2761,6 +2762,36 @@
   </x:si>
   <x:si>
     <x:t>1216192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHRISTOPHER P. RODA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Kahayag, Dumagoc, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0719-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1411-353</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBEN S. TAMULA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DISTRICT KAWASHI, POBLACION, Tabina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1316-24(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1394-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216214</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -6858,6 +6889,1284 @@
     <x:mergeCell ref="B77:E77"/>
     <x:mergeCell ref="B78:E78"/>
     <x:mergeCell ref="B79:E79"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="s">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="s">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L8" s="17">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="s">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="18" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="920">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="929">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2762,6 +2762,33 @@
   </x:si>
   <x:si>
     <x:t>1216192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yoho Building Purok tambis, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-07290-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1402-161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quezon avenue, poblacion, Sindangan, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-07286-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1401-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216209</x:t>
   </x:si>
   <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
@@ -7062,13 +7089,13 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
         <x:v>910</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E8" s="13" t="s">
         <x:v>911</x:v>
@@ -7080,19 +7107,19 @@
         <x:v>913</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46115</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>914</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="17">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>27</x:v>
@@ -7100,89 +7127,173 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="s">
         <x:v>915</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="13" t="s">
+      <x:c r="F9" s="13" t="s">
         <x:v>916</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>917</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46097.2826708912</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46097.2826882292</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
         <x:v>918</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="s">
-        <x:v>919</x:v>
-      </x:c>
       <x:c r="K9" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46119.1491368056</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="s">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L10" s="17">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="s">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="H11" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L11" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M11" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="24" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8159,14 +8270,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="929">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="939">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2764,6 +2764,21 @@
     <x:t>1216192</x:t>
   </x:si>
   <x:si>
+    <x:t>LEONILO V. MARTEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK SANTAN, BALANGASAN, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AT-II-91634-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1415-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216220</x:t>
+  </x:si>
+  <x:si>
     <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -2789,6 +2804,21 @@
   </x:si>
   <x:si>
     <x:t>1216209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR bldg. Rizal avenue, San francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0716-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1296-085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216221</x:t>
   </x:si>
   <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
@@ -7089,13 +7119,13 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
-        <x:v>366</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C8" s="13" t="s">
         <x:v>910</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="13" t="s">
         <x:v>911</x:v>
@@ -7107,19 +7137,19 @@
         <x:v>913</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46097.2931531944</x:v>
+        <x:v>46104.0644558912</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46097.2931710069</x:v>
+        <x:v>45902</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>914</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="L8" s="17">
-        <x:v>46119.1505964699</x:v>
+        <x:v>46120.3413710417</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>27</x:v>
@@ -7130,34 +7160,34 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>910</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
-        <x:v>915</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="F9" s="13" t="s">
-        <x:v>916</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="G9" s="13" t="s">
-        <x:v>917</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46097.2826708912</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46097.2826882292</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
-        <x:v>918</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46119.1491368056</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>27</x:v>
@@ -7165,13 +7195,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>919</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
         <x:v>920</x:v>
@@ -7183,19 +7213,19 @@
         <x:v>922</x:v>
       </x:c>
       <x:c r="H10" s="15">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46097.2826708912</x:v>
       </x:c>
       <x:c r="I10" s="15">
-        <x:v>46115</x:v>
+        <x:v>46097.2826882292</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
         <x:v>923</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="17">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46119.1491368056</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
         <x:v>27</x:v>
@@ -7203,7 +7233,7 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
         <x:v>924</x:v>
@@ -7221,83 +7251,177 @@
         <x:v>927</x:v>
       </x:c>
       <x:c r="H11" s="15">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46049.1592238657</x:v>
       </x:c>
       <x:c r="I11" s="15">
-        <x:v>46123</x:v>
+        <x:v>45939</x:v>
       </x:c>
       <x:c r="J11" s="14" t="s">
         <x:v>928</x:v>
       </x:c>
       <x:c r="K11" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="17">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46120.3467831597</x:v>
       </x:c>
       <x:c r="M11" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="s">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>932</x:v>
+      </x:c>
+      <x:c r="H12" s="15">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
+        <x:v>933</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L12" s="17">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="s">
+        <x:v>934</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="s">
+        <x:v>935</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="H13" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L13" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="20" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="20" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="s">
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="24" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8270,15 +8394,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="939">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="944">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2777,6 +2777,21 @@
   </x:si>
   <x:si>
     <x:t>1216220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Hypermarket Rizal Avenue, Blancia, Molave, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-07277-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1400-190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216222</x:t>
   </x:si>
   <x:si>
     <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
@@ -7157,7 +7172,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
-        <x:v>366</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
         <x:v>915</x:v>
@@ -7175,19 +7190,19 @@
         <x:v>918</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46097.2931531944</x:v>
+        <x:v>46097.2573180208</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46097.2931710069</x:v>
+        <x:v>46097.2573345602</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
         <x:v>919</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46119.1505964699</x:v>
+        <x:v>46125.2485400116</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>27</x:v>
@@ -7198,34 +7213,34 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>915</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
-        <x:v>920</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="F10" s="13" t="s">
-        <x:v>921</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="G10" s="13" t="s">
-        <x:v>922</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="H10" s="15">
-        <x:v>46097.2826708912</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I10" s="15">
-        <x:v>46097.2826882292</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
-        <x:v>923</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="17">
-        <x:v>46119.1491368056</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
         <x:v>27</x:v>
@@ -7233,13 +7248,13 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>924</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
         <x:v>925</x:v>
@@ -7251,19 +7266,19 @@
         <x:v>927</x:v>
       </x:c>
       <x:c r="H11" s="15">
-        <x:v>46049.1592238657</x:v>
+        <x:v>46097.2826708912</x:v>
       </x:c>
       <x:c r="I11" s="15">
-        <x:v>45939</x:v>
+        <x:v>46097.2826882292</x:v>
       </x:c>
       <x:c r="J11" s="14" t="s">
         <x:v>928</x:v>
       </x:c>
       <x:c r="K11" s="16" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="17">
-        <x:v>46120.3467831597</x:v>
+        <x:v>46119.1491368056</x:v>
       </x:c>
       <x:c r="M11" s="13" t="s">
         <x:v>27</x:v>
@@ -7271,7 +7286,7 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="13" t="s">
         <x:v>929</x:v>
@@ -7289,19 +7304,19 @@
         <x:v>932</x:v>
       </x:c>
       <x:c r="H12" s="15">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46049.1592238657</x:v>
       </x:c>
       <x:c r="I12" s="15">
-        <x:v>46115</x:v>
+        <x:v>45939</x:v>
       </x:c>
       <x:c r="J12" s="14" t="s">
         <x:v>933</x:v>
       </x:c>
       <x:c r="K12" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L12" s="17">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46120.3467831597</x:v>
       </x:c>
       <x:c r="M12" s="13" t="s">
         <x:v>27</x:v>
@@ -7327,10 +7342,10 @@
         <x:v>937</x:v>
       </x:c>
       <x:c r="H13" s="15">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46100.1333120023</x:v>
       </x:c>
       <x:c r="I13" s="15">
-        <x:v>46123</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J13" s="14" t="s">
         <x:v>938</x:v>
@@ -7339,59 +7354,86 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L13" s="17">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46118.9999416204</x:v>
       </x:c>
       <x:c r="M13" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="s">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L14" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="20" t="s"/>
-      <x:c r="F16" s="20" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="20" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="s">
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="s">
         <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="24" t="s">
-        <x:v>366</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C19" s="25" t="s"/>
       <x:c r="D19" s="25" t="s"/>
       <x:c r="E19" s="25" t="s"/>
       <x:c r="F19" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="24" t="s">
-        <x:v>13</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C20" s="25" t="s"/>
       <x:c r="D20" s="25" t="s"/>
@@ -7402,7 +7444,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="24" t="s">
-        <x:v>21</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C21" s="25" t="s"/>
       <x:c r="D21" s="25" t="s"/>
@@ -7411,19 +7453,39 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="27" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8394,17 +8456,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="944">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="948">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2849,6 +2849,18 @@
   </x:si>
   <x:si>
     <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOEMA M.MORGIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1022-19(MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1429-605</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216224</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN S. TAMULA</x:t>
@@ -7371,69 +7383,96 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
         <x:v>940</x:v>
       </x:c>
-      <x:c r="F14" s="13" t="s">
+      <x:c r="G14" s="13" t="s">
         <x:v>941</x:v>
       </x:c>
-      <x:c r="G14" s="13" t="s">
+      <x:c r="H14" s="15">
+        <x:v>46107.098771794</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46161</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
         <x:v>942</x:v>
       </x:c>
-      <x:c r="H14" s="15">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I14" s="15">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J14" s="14" t="s">
-        <x:v>943</x:v>
-      </x:c>
       <x:c r="K14" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L14" s="17">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1382984606</x:v>
       </x:c>
       <x:c r="M14" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L15" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="20" t="s"/>
-      <x:c r="F17" s="20" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="20" t="s"/>
+      <x:c r="F18" s="20" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="s">
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="s">
         <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="24" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="24" t="s">
-        <x:v>76</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C20" s="25" t="s"/>
       <x:c r="D20" s="25" t="s"/>
@@ -7444,49 +7483,59 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="24" t="s">
-        <x:v>366</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C21" s="25" t="s"/>
       <x:c r="D21" s="25" t="s"/>
       <x:c r="E21" s="25" t="s"/>
       <x:c r="F21" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="24" t="s">
-        <x:v>13</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C22" s="25" t="s"/>
       <x:c r="D22" s="25" t="s"/>
       <x:c r="E22" s="25" t="s"/>
       <x:c r="F22" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="24" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C23" s="25" t="s"/>
       <x:c r="D23" s="25" t="s"/>
       <x:c r="E23" s="25" t="s"/>
       <x:c r="F23" s="26" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="24" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8460,14 +8509,14 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="948">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="970">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -2836,6 +2836,39 @@
     <x:t>1216221</x:t>
   </x:si>
   <x:si>
+    <x:t>AMANUDIN U.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1020-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1431-614</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1017-19(REN/MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1418-218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMANUDIN UNGAD BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1018-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1413-402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216223</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
   </x:si>
   <x:si>
@@ -2851,6 +2884,27 @@
     <x:t>1216212</x:t>
   </x:si>
   <x:si>
+    <x:t>NOEMA M.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1019-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1430-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1016-19(DUP/REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1419-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216226</x:t>
+  </x:si>
+  <x:si>
     <x:t>NOEMA M.MORGIA</x:t>
   </x:si>
   <x:si>
@@ -2876,6 +2930,18 @@
   </x:si>
   <x:si>
     <x:t>1216214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOHNRIN ROSALIJOS GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21-SROPIX-13838</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1432-568</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216229</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -7345,28 +7411,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
         <x:v>935</x:v>
       </x:c>
-      <x:c r="F13" s="13" t="s">
+      <x:c r="G13" s="13" t="s">
         <x:v>936</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="s">
+      <x:c r="H13" s="15">
+        <x:v>46107.1169023495</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
         <x:v>937</x:v>
-      </x:c>
-      <x:c r="H13" s="15">
-        <x:v>46100.1333120023</x:v>
-      </x:c>
-      <x:c r="I13" s="15">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J13" s="14" t="s">
-        <x:v>938</x:v>
       </x:c>
       <x:c r="K13" s="16" t="n">
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L13" s="17">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46126.1914953241</x:v>
       </x:c>
       <x:c r="M13" s="13" t="s">
         <x:v>27</x:v>
@@ -7377,7 +7443,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="13" t="s">
-        <x:v>939</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="D14" s="14" t="s">
         <x:v>15</x:v>
@@ -7386,25 +7452,25 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="F14" s="13" t="s">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>46105.2495215509</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
         <x:v>940</x:v>
       </x:c>
-      <x:c r="G14" s="13" t="s">
-        <x:v>941</x:v>
-      </x:c>
-      <x:c r="H14" s="15">
-        <x:v>46107.098771794</x:v>
-      </x:c>
-      <x:c r="I14" s="15">
-        <x:v>46161</x:v>
-      </x:c>
-      <x:c r="J14" s="14" t="s">
-        <x:v>942</x:v>
-      </x:c>
       <x:c r="K14" s="16" t="n">
-        <x:v>1470</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="L14" s="17">
-        <x:v>46126.1382984606</x:v>
+        <x:v>46126.1951014005</x:v>
       </x:c>
       <x:c r="M14" s="13" t="s">
         <x:v>27</x:v>
@@ -7415,134 +7481,366 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="13" t="s">
-        <x:v>943</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>46102.5247719444</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
         <x:v>944</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>945</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>946</x:v>
-      </x:c>
-      <x:c r="H15" s="15">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I15" s="15">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J15" s="14" t="s">
-        <x:v>947</x:v>
-      </x:c>
       <x:c r="K15" s="16" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L15" s="17">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1550669907</x:v>
       </x:c>
       <x:c r="M15" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="H16" s="15">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I16" s="15">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L16" s="17">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>952</x:v>
+      </x:c>
+      <x:c r="H17" s="15">
+        <x:v>46107.1054781366</x:v>
+      </x:c>
+      <x:c r="I17" s="15">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="s">
+        <x:v>953</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L17" s="17">
+        <x:v>46126.1858600463</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="18" t="s">
+      <x:c r="B18" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="H18" s="15">
+        <x:v>46107.0809005093</x:v>
+      </x:c>
+      <x:c r="I18" s="15">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="s">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L18" s="17">
+        <x:v>46126.1597197801</x:v>
+      </x:c>
+      <x:c r="M18" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>957</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="H19" s="15">
+        <x:v>46107.098771794</x:v>
+      </x:c>
+      <x:c r="I19" s="15">
+        <x:v>46161</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="s">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L19" s="17">
+        <x:v>46126.1382984606</x:v>
+      </x:c>
+      <x:c r="M19" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>962</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="H20" s="15">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I20" s="15">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="s">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L20" s="17">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="H21" s="15">
+        <x:v>46107.1249875579</x:v>
+      </x:c>
+      <x:c r="I21" s="15">
+        <x:v>45842</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="s">
+        <x:v>969</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L21" s="17">
+        <x:v>46126.1994933218</x:v>
+      </x:c>
+      <x:c r="M21" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="18" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="s"/>
-      <x:c r="D18" s="19" t="s"/>
-      <x:c r="E18" s="20" t="s"/>
-      <x:c r="F18" s="20" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="C24" s="19" t="s"/>
+      <x:c r="D24" s="19" t="s"/>
+      <x:c r="E24" s="20" t="s"/>
+      <x:c r="F24" s="20" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="s">
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="24" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="24" t="s">
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="24" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="24" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="24" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="24" t="s">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="27" t="s">
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="24" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8505,18 +8803,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
